--- a/tame_output/ON/bt/strategyON_20240417.xlsx
+++ b/tame_output/ON/bt/strategyON_20240417.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119.2%</t>
+          <t>118.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-722.5%</t>
+          <t>-736.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.4%</t>
+          <t>-58.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.0%</t>
+          <t>780.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-561.7%</t>
+          <t>-562.2%</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.6%</t>
+          <t>-289.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.7%</t>
+          <t>-46.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-230.3%</t>
+          <t>-230.5%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,11 +1285,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-39.4%</t>
+          <t>-40.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.0%</t>
+          <t>-159.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-255.7%</t>
+          <t>-256.2%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-159.0%</t>
+          <t>-159.3%</t>
         </is>
       </c>
     </row>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923088</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234391</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860581</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.39868398140562</v>
+        <v>-12.53815648711955</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.793558456119</v>
+        <v>-1.849347458404573</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.727313387683918</v>
+        <v>-3.909001576609002</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9298835281466458</v>
+        <v>0.8208706147915952</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.17283882868621</v>
+        <v>-12.31231133440014</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.693641321995027</v>
+        <v>-1.7494303242806</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.685386712096754</v>
+        <v>-3.867074901021838</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.9646186065351525</v>
+        <v>0.8556056931801019</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.88656401636351</v>
+        <v>-12.02603652207745</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.57799225250989</v>
+        <v>-1.633781254795463</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.685386712096754</v>
+        <v>-3.867074901021838</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.9657577510912114</v>
+        <v>0.8567448377361608</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.9394593044078</v>
+        <v>-12.07893181012173</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.596516593565497</v>
+        <v>-1.65230559585107</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.680431366008308</v>
+        <v>-3.862119554933392</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.9713647329063866</v>
+        <v>0.8623518195513364</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.65555057347905</v>
+        <v>-11.79502307919299</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.477219396955361</v>
+        <v>-1.533008399240933</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.680431366008308</v>
+        <v>-3.862119554933392</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.9770984371450231</v>
+        <v>0.8680855237899729</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.4085633232861</v>
+        <v>-11.54803582900003</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.388161759272045</v>
+        <v>-1.443950761557618</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.61513230474044</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.115553524866929</v>
+        <v>1.006540611511879</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.14472645608203</v>
+        <v>-11.28419896179596</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.292510493703325</v>
+        <v>-1.348299495988898</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.61513230474044</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.105670043554022</v>
+        <v>0.9966571301989711</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.87748465521363</v>
+        <v>-11.01695716092757</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.187448333855339</v>
+        <v>-1.243237336140913</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.61513230474044</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.103835483054648</v>
+        <v>0.9948225696995974</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.60167549181315</v>
+        <v>-10.74114799752708</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.077424983468606</v>
+        <v>-1.13321398575418</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.344424807536623</v>
+        <v>-3.526112996461706</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.156946753048427</v>
+        <v>1.047933839693377</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.57772195083719</v>
+        <v>-10.71719445655112</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.067175060932729</v>
+        <v>-1.122964063218303</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.320471266560665</v>
+        <v>-3.502159455485749</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.171987383779495</v>
+        <v>1.062974470424445</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.31366201251439</v>
+        <v>-10.45313451822833</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9748114017653631</v>
+        <v>-1.030600404050936</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.056411328237869</v>
+        <v>-3.238099517162953</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.317163030611421</v>
+        <v>1.20815011725637</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.606582389009557</v>
+        <v>-9.746054894723489</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6947665860237291</v>
+        <v>-0.750555588309302</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.056411328237869</v>
+        <v>-3.238099517162953</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.31437599695112</v>
+        <v>1.20536308359607</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.566398090643366</v>
+        <v>-9.705870596357299</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6783492427894116</v>
+        <v>-0.7341382450749845</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.016227029871678</v>
+        <v>-3.197915218796762</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.338830199858676</v>
+        <v>1.229817286503625</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.486328295105562</v>
+        <v>-9.625800800819494</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6469545033535327</v>
+        <v>-0.7027435056391056</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.936157234333874</v>
+        <v>-3.117845423258958</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.386238898402115</v>
+        <v>1.277225985047065</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.252847072875962</v>
+        <v>-9.392319578589895</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5456375856238407</v>
+        <v>-0.6014265879094136</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.702676012104276</v>
+        <v>-2.88436420102936</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.534252060577727</v>
+        <v>1.425239147222676</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.073138542732089</v>
+        <v>-9.212611048446021</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4766463838792503</v>
+        <v>-0.5324353861648232</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.64550450794158</v>
+        <v>-2.827192696866664</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.565662752762385</v>
+        <v>1.456649839407335</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.940863069101201</v>
+        <v>-9.080335574815134</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4283687076798683</v>
+        <v>-0.4841577099654413</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.513229034310693</v>
+        <v>-2.694917223235777</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.640395523687944</v>
+        <v>1.531382610332894</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.750263394428048</v>
+        <v>-8.88973590014198</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3493137771229704</v>
+        <v>-0.4051027794085433</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.322629359637541</v>
+        <v>-2.504317548562625</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.757570389179472</v>
+        <v>1.648557475824422</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.501263595744467</v>
+        <v>-8.640736101458399</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2368075164258792</v>
+        <v>-0.2925965187114521</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.322629359637541</v>
+        <v>-2.504317548562625</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.770476730403131</v>
+        <v>1.66146381704808</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.606853585517571</v>
+        <v>-8.746326091231504</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4070194419343398</v>
+        <v>-0.4628084442199127</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.428219349410645</v>
+        <v>-2.609907538335729</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.579146806940049</v>
+        <v>1.470133893584999</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.625588487636168</v>
+        <v>-8.765060993350101</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3659690609046922</v>
+        <v>-0.4217580631902651</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.428219349410645</v>
+        <v>-2.609907538335729</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.627691148817136</v>
+        <v>1.518678235462086</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.348850312965356</v>
+        <v>-8.488322818679288</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2518947790503723</v>
+        <v>-0.3076837813359452</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.246402688300719</v>
+        <v>-2.428090877225803</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.740160157469086</v>
+        <v>1.631147244114036</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.221957906530285</v>
+        <v>-8.361430412244218</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2098518027298222</v>
+        <v>-0.2656408050153956</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.119510281865649</v>
+        <v>-2.301198470790733</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.80758161507665</v>
+        <v>1.698568701721599</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.178409499759594</v>
+        <v>-8.317882005473527</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1993930521166392</v>
+        <v>-0.2551820544022121</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.119510281865649</v>
+        <v>-2.301198470790733</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.800621002981557</v>
+        <v>1.691608089626506</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.936261106305736</v>
+        <v>-8.075733612019668</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.08807134035395281</v>
+        <v>-0.1438603426395257</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.119510281865649</v>
+        <v>-2.301198470790733</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.8150833573627</v>
+        <v>1.706070444007649</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192812</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.873031734537387</v>
+        <v>-8.012504240251321</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.06824747118741836</v>
+        <v>-0.1240364734729917</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.119510281865649</v>
+        <v>-2.301198470790733</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.809615477821895</v>
+        <v>1.700602564466844</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.686544042160381</v>
+        <v>-7.826016547874315</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.003845699773961098</v>
+        <v>-0.05194330251161228</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.933022589488643</v>
+        <v>-2.114710778413727</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.919006187258675</v>
+        <v>1.809993273903625</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.665394843256938</v>
+        <v>-7.804867348970872</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.02000635757266389</v>
+        <v>-0.03578264471290948</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.9118733905852</v>
+        <v>-2.093561579510284</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.939396684838067</v>
+        <v>1.830383771483016</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788089</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.421629401273494</v>
+        <v>-7.561101906987427</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1132932427130924</v>
+        <v>0.057504240427519</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.9118733905852</v>
+        <v>-2.093561579510284</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.935177393185118</v>
+        <v>1.826164479830067</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.157601334080233</v>
+        <v>-7.297073839794168</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2210287835104126</v>
+        <v>0.1652397812248387</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.710007991769246</v>
+        <v>-1.89169618069433</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.058420946394706</v>
+        <v>1.949408033039655</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.907750940131159</v>
+        <v>-7.047223445845093</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3137110160737446</v>
+        <v>0.2579220137881708</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.710007991769246</v>
+        <v>-1.89169618069433</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.051163021378408</v>
+        <v>1.942150108023357</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.60418345112718</v>
+        <v>-6.743655956841114</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4387371351959848</v>
+        <v>0.382948132910411</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.710007991769246</v>
+        <v>-1.89169618069433</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.054762144899057</v>
+        <v>1.945749231544006</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862983</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.530703542275166</v>
+        <v>-6.6701760479891</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4814566047913442</v>
+        <v>0.4256676025057704</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.636528082917232</v>
+        <v>-1.818216271842316</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.112177596264819</v>
+        <v>2.003164682909769</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102778</v>
+        <v>3.77376164710278</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.305670542606343</v>
+        <v>-6.445143048320277</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5704902822751703</v>
+        <v>0.5147012799895965</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.411495083248409</v>
+        <v>-1.593183272173493</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.24621787368241</v>
+        <v>2.137204960327359</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.091036164969936</v>
+        <v>-6.230508670683871</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6610388343840503</v>
+        <v>0.6052498320984765</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.196860705612002</v>
+        <v>-1.378548894537087</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.379693301318571</v>
+        <v>2.27068038796352</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.824435807995584</v>
+        <v>-5.963908313709519</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7488732359575865</v>
+        <v>0.6930842336720131</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.196860705612002</v>
+        <v>-1.378548894537087</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.360887560102367</v>
+        <v>2.251874646747316</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712292</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.584005311190724</v>
+        <v>-5.723477816904659</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8467885113044082</v>
+        <v>0.7909995090188344</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9564302088071419</v>
+        <v>-1.138118397732226</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.50688893481016</v>
+        <v>2.39787602145511</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837682</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.341214503541279</v>
+        <v>-5.480687009255213</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9478341481990067</v>
+        <v>0.8920451459134329</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9564302088071419</v>
+        <v>-1.138118397732226</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.510818248644981</v>
+        <v>2.40180533528993</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.10160941193419</v>
+        <v>-5.241081917648124</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.044354768759182</v>
+        <v>0.9885657664736085</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8893822611386474</v>
+        <v>-1.071070450063732</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.551725601163417</v>
+        <v>2.442712687808366</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972337</v>
+        <v>3.848613050972339</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.858953823511026</v>
+        <v>-4.99842632922496</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.138415075348441</v>
+        <v>1.082626073062867</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8893822611386474</v>
+        <v>-1.071070450063732</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.548723672383411</v>
+        <v>2.43971075902836</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.638933025474016</v>
+        <v>-4.77840553118795</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.228002431573859</v>
+        <v>1.172213429288286</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7481624160706671</v>
+        <v>-0.9298506049957516</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.635034616434813</v>
+        <v>2.526021703079762</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.439684395569206</v>
+        <v>-4.579156901283141</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.323596066337606</v>
+        <v>1.267807064052033</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7481624160706671</v>
+        <v>-0.9298506049957516</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.650928799236636</v>
+        <v>2.541915885881585</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.280169292049837</v>
+        <v>-4.419641797763771</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.388547952185656</v>
+        <v>1.332758949900082</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5886473125512972</v>
+        <v>-0.7703355014763816</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.74778370578856</v>
+        <v>2.63877079243351</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046992</v>
+        <v>3.791269976046994</v>
       </c>
       <c r="C1932" t="n">
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.135497146950099</v>
+        <v>-4.274969652664034</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.456504912786991</v>
+        <v>1.400715910501417</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4439751674515598</v>
+        <v>-0.6256633563766443</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.844675095409842</v>
+        <v>2.735662182054792</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412101</v>
       </c>
       <c r="C1933" t="n">
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.117727688019143</v>
+        <v>-4.257200193733078</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.378952388446095</v>
+        <v>1.323163386160521</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4262057085206042</v>
+        <v>-0.6078938974456887</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.770676462855137</v>
+        <v>2.661663549500087</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.030928190240134</v>
+        <v>-4.170400695954068</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.436072680880265</v>
+        <v>1.380283678594691</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4262057085206042</v>
+        <v>-0.6078938974456887</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.793076956177703</v>
+        <v>2.684064042822653</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900692</v>
       </c>
       <c r="C1935" t="n">
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.931235575511122</v>
+        <v>-4.070708081225057</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.476022128145282</v>
+        <v>1.420233125859708</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3265130937915925</v>
+        <v>-0.5082012827166769</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.852964926388522</v>
+        <v>2.743952013033472</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.720821296755446</v>
+        <v>3.389609180356693</v>
       </c>
       <c r="C1936" t="n">
         <v>3.05987970513818</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.001378552744525</v>
+        <v>-4.006249754123279</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.458971859726623</v>
+        <v>1.457023379175121</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.316741586862327</v>
+        <v>-0.3218596756917605</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.869834753020784</v>
+        <v>2.866763899723124</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240417.xlsx
+++ b/tame_output/ON/bt/strategyON_20240417.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.9%</t>
+          <t>119.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-736.4%</t>
+          <t>-722.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.9%</t>
+          <t>-58.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>780.8%</t>
+          <t>788.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-562.2%</t>
+          <t>-561.5%</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-289.2%</t>
+          <t>-283.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-46.1%</t>
+          <t>-45.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-230.5%</t>
+          <t>-230.3%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,11 +1285,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-39.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.5%</t>
+          <t>-160.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-256.2%</t>
+          <t>-256.3%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-159.3%</t>
+          <t>-159.4%</t>
         </is>
       </c>
     </row>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923088</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860581</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.53815648711955</v>
+        <v>-12.39868398140562</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.849347458404573</v>
+        <v>-1.793558456119</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.909001576609002</v>
+        <v>-3.727313387683918</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.8208706147915952</v>
+        <v>0.9298835281466458</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.31231133440014</v>
+        <v>-12.17283882868621</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.7494303242806</v>
+        <v>-1.693641321995027</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.867074901021838</v>
+        <v>-3.685386712096754</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.8556056931801019</v>
+        <v>0.9646186065351525</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-12.02603652207745</v>
+        <v>-11.88656401636351</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.633781254795463</v>
+        <v>-1.57799225250989</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.867074901021838</v>
+        <v>-3.685386712096754</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.8567448377361608</v>
+        <v>0.9657577510912114</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-12.07893181012173</v>
+        <v>-11.9394593044078</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.65230559585107</v>
+        <v>-1.596516593565497</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.862119554933392</v>
+        <v>-3.680431366008308</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.8623518195513364</v>
+        <v>0.9713647329063866</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.79502307919299</v>
+        <v>-11.65555057347905</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.533008399240933</v>
+        <v>-1.477219396955361</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.862119554933392</v>
+        <v>-3.680431366008308</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.8680855237899729</v>
+        <v>0.9770984371450231</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.54803582900003</v>
+        <v>-11.4085633232861</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.443950761557618</v>
+        <v>-1.388161759272045</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.61513230474044</v>
+        <v>-3.433444115815356</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.006540611511879</v>
+        <v>1.115553524866929</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.28419896179596</v>
+        <v>-11.14472645608203</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.348299495988898</v>
+        <v>-1.292510493703325</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.61513230474044</v>
+        <v>-3.433444115815356</v>
       </c>
       <c r="G1895" t="n">
-        <v>0.9966571301989711</v>
+        <v>1.105670043554022</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-11.01695716092757</v>
+        <v>-10.87748465521363</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.243237336140913</v>
+        <v>-1.187448333855339</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.61513230474044</v>
+        <v>-3.433444115815356</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.9948225696995974</v>
+        <v>1.103835483054648</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.74114799752708</v>
+        <v>-10.60167549181315</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.13321398575418</v>
+        <v>-1.077424983468606</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.526112996461706</v>
+        <v>-3.344424807536623</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.047933839693377</v>
+        <v>1.156946753048427</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.71719445655112</v>
+        <v>-10.57772195083719</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.122964063218303</v>
+        <v>-1.067175060932729</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.502159455485749</v>
+        <v>-3.320471266560665</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.062974470424445</v>
+        <v>1.171987383779495</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.45313451822833</v>
+        <v>-10.31366201251439</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.030600404050936</v>
+        <v>-0.9748114017653631</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.238099517162953</v>
+        <v>-3.056411328237869</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.20815011725637</v>
+        <v>1.317163030611421</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.746054894723489</v>
+        <v>-9.606582389009557</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.750555588309302</v>
+        <v>-0.6947665860237291</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.238099517162953</v>
+        <v>-3.056411328237869</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.20536308359607</v>
+        <v>1.31437599695112</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.705870596357299</v>
+        <v>-9.566398090643366</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7341382450749845</v>
+        <v>-0.6783492427894116</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.197915218796762</v>
+        <v>-3.016227029871678</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.229817286503625</v>
+        <v>1.338830199858676</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.625800800819494</v>
+        <v>-9.486328295105562</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7027435056391056</v>
+        <v>-0.6469545033535327</v>
       </c>
       <c r="F1902" t="n">
-        <v>-3.117845423258958</v>
+        <v>-2.936157234333874</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.277225985047065</v>
+        <v>1.386238898402115</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.392319578589895</v>
+        <v>-9.252847072875962</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6014265879094136</v>
+        <v>-0.5456375856238407</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.88436420102936</v>
+        <v>-2.702676012104276</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.425239147222676</v>
+        <v>1.534252060577727</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.212611048446021</v>
+        <v>-9.073138542732089</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5324353861648232</v>
+        <v>-0.4766463838792503</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.827192696866664</v>
+        <v>-2.64550450794158</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.456649839407335</v>
+        <v>1.565662752762385</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.080335574815134</v>
+        <v>-8.940863069101201</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4841577099654413</v>
+        <v>-0.4283687076798683</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.694917223235777</v>
+        <v>-2.513229034310693</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.531382610332894</v>
+        <v>1.640395523687944</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.88973590014198</v>
+        <v>-8.750263394428048</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4051027794085433</v>
+        <v>-0.3493137771229704</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.504317548562625</v>
+        <v>-2.322629359637541</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.648557475824422</v>
+        <v>1.757570389179472</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.640736101458399</v>
+        <v>-8.501263595744467</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2925965187114521</v>
+        <v>-0.2368075164258792</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.504317548562625</v>
+        <v>-2.322629359637541</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.66146381704808</v>
+        <v>1.770476730403131</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.746326091231504</v>
+        <v>-8.606853585517571</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4628084442199127</v>
+        <v>-0.4070194419343398</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.609907538335729</v>
+        <v>-2.428219349410645</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.470133893584999</v>
+        <v>1.579146806940049</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.765060993350101</v>
+        <v>-8.625588487636168</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4217580631902651</v>
+        <v>-0.3659690609046922</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.609907538335729</v>
+        <v>-2.433815359070776</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.518678235462086</v>
+        <v>1.624333543021057</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.488322818679288</v>
+        <v>-8.348850312965356</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3076837813359452</v>
+        <v>-0.2518947790503723</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.428090877225803</v>
+        <v>-2.25199869796085</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.631147244114036</v>
+        <v>1.736802551673007</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.361430412244218</v>
+        <v>-8.221957906530285</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2656408050153956</v>
+        <v>-0.2098518027298222</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.301198470790733</v>
+        <v>-2.125106291525781</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.698568701721599</v>
+        <v>1.804224009280571</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.317882005473527</v>
+        <v>-8.178409499759594</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2551820544022121</v>
+        <v>-0.1993930521166392</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.301198470790733</v>
+        <v>-2.125106291525781</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.691608089626506</v>
+        <v>1.797263397185478</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.075733612019668</v>
+        <v>-7.936261106305736</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1438603426395257</v>
+        <v>-0.08807134035395281</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.301198470790733</v>
+        <v>-2.125106291525781</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.706070444007649</v>
+        <v>1.811725751566621</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.012504240251321</v>
+        <v>-7.873031734537387</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1240364734729917</v>
+        <v>-0.06824747118741836</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.301198470790733</v>
+        <v>-2.125106291525781</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.700602564466844</v>
+        <v>1.806257872025816</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.826016547874315</v>
+        <v>-7.686544042160381</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.05194330251161228</v>
+        <v>0.003845699773961098</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.114710778413727</v>
+        <v>-1.938618599148774</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.809993273903625</v>
+        <v>1.915648581462597</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.804867348970872</v>
+        <v>-7.665394843256938</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.03578264471290948</v>
+        <v>0.02000635757266389</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.093561579510284</v>
+        <v>-1.917469400245331</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.830383771483016</v>
+        <v>1.936039079041988</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788089</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.561101906987427</v>
+        <v>-7.421629401273494</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.057504240427519</v>
+        <v>0.1132932427130924</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.093561579510284</v>
+        <v>-1.917469400245331</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.826164479830067</v>
+        <v>1.931819787389039</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.297073839794168</v>
+        <v>-7.157601334080233</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1652397812248387</v>
+        <v>0.2210287835104126</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.89169618069433</v>
+        <v>-1.715604001429377</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.949408033039655</v>
+        <v>2.055063340598627</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.047223445845093</v>
+        <v>-6.907750940131159</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2579220137881708</v>
+        <v>0.3137110160737446</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.89169618069433</v>
+        <v>-1.715604001429377</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.942150108023357</v>
+        <v>2.047805415582329</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.743655956841114</v>
+        <v>-6.60418345112718</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.382948132910411</v>
+        <v>0.4387371351959848</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.89169618069433</v>
+        <v>-1.715604001429377</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.945749231544006</v>
+        <v>2.051404539102978</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862983</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.6701760479891</v>
+        <v>-6.530703542275166</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4256676025057704</v>
+        <v>0.4814566047913442</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.818216271842316</v>
+        <v>-1.642124092577363</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.003164682909769</v>
+        <v>2.10881999046874</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376164710278</v>
+        <v>3.773761647102778</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.445143048320277</v>
+        <v>-6.305670542606343</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5147012799895965</v>
+        <v>0.5704902822751703</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.593183272173493</v>
+        <v>-1.41709109290854</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.137204960327359</v>
+        <v>2.242860267886331</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.230508670683871</v>
+        <v>-6.091036164969936</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6052498320984765</v>
+        <v>0.6610388343840503</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.378548894537087</v>
+        <v>-1.202456715272133</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.27068038796352</v>
+        <v>2.376335695522493</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.963908313709519</v>
+        <v>-5.824435807995584</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6930842336720131</v>
+        <v>0.7488732359575865</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.378548894537087</v>
+        <v>-1.202456715272133</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.251874646747316</v>
+        <v>2.357529954306288</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712292</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.723477816904659</v>
+        <v>-5.584005311190724</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7909995090188344</v>
+        <v>0.8467885113044082</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.138118397732226</v>
+        <v>-0.962026218467273</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.39787602145511</v>
+        <v>2.503531329014081</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837682</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.480687009255213</v>
+        <v>-5.341214503541279</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8920451459134329</v>
+        <v>0.9478341481990067</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.138118397732226</v>
+        <v>-0.962026218467273</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.40180533528993</v>
+        <v>2.507460642848902</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.241081917648124</v>
+        <v>-5.10160941193419</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9885657664736085</v>
+        <v>1.044354768759182</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.071070450063732</v>
+        <v>-0.8949782707987785</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.442712687808366</v>
+        <v>2.548367995367339</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972339</v>
+        <v>3.848613050972337</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.99842632922496</v>
+        <v>-4.858953823511026</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.082626073062867</v>
+        <v>1.138415075348441</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.071070450063732</v>
+        <v>-0.8949782707987785</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.43971075902836</v>
+        <v>2.545366066587332</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.77840553118795</v>
+        <v>-4.638933025474016</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.172213429288286</v>
+        <v>1.228002431573859</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9298506049957516</v>
+        <v>-0.7537584257307982</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.526021703079762</v>
+        <v>2.631677010638734</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.579156901283141</v>
+        <v>-4.439684395569206</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.267807064052033</v>
+        <v>1.323596066337606</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9298506049957516</v>
+        <v>-0.7537584257307982</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.541915885881585</v>
+        <v>2.647571193440557</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.419641797763771</v>
+        <v>-4.280169292049837</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.332758949900082</v>
+        <v>1.388547952185656</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7703355014763816</v>
+        <v>-0.5942433222114283</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.63877079243351</v>
+        <v>2.744426099992481</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046994</v>
+        <v>3.791269976046992</v>
       </c>
       <c r="C1932" t="n">
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.274969652664034</v>
+        <v>-4.135497146950099</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.400715910501417</v>
+        <v>1.456504912786991</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6256633563766443</v>
+        <v>-0.4495711771116909</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.735662182054792</v>
+        <v>2.841317489613764</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412101</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.257200193733078</v>
+        <v>-4.117727688019143</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.323163386160521</v>
+        <v>1.378952388446095</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6078938974456887</v>
+        <v>-0.4318017181807353</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.661663549500087</v>
+        <v>2.767318857059059</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.170400695954068</v>
+        <v>-4.030928190240134</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.380283678594691</v>
+        <v>1.436072680880265</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6078938974456887</v>
+        <v>-0.4318017181807353</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.684064042822653</v>
+        <v>2.789719350381625</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900692</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.070708081225057</v>
+        <v>-3.931235575511122</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.420233125859708</v>
+        <v>1.476022128145282</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5082012827166769</v>
+        <v>-0.3321091034517236</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.743952013033472</v>
+        <v>2.849607320592444</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.389609180356693</v>
+        <v>3.736083384562804</v>
       </c>
       <c r="C1936" t="n">
         <v>3.05987970513818</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.006249754123279</v>
+        <v>-3.999605761835132</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.457023379175121</v>
+        <v>1.45968097609038</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3218596756917605</v>
+        <v>-0.3228334044155086</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.866763899723124</v>
+        <v>2.866179662488875</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240417.xlsx
+++ b/tame_output/ON/bt/strategyON_20240417.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>10.9%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119.2%</t>
+          <t>118.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-722.5%</t>
+          <t>-736.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.4%</t>
+          <t>-58.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>98.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.3%</t>
+          <t>780.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-561.5%</t>
+          <t>-575.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.6%</t>
+          <t>-289.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.7%</t>
+          <t>-46.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-230.3%</t>
+          <t>-235.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,11 +1285,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-39.4%</t>
+          <t>-40.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.0%</t>
+          <t>-159.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-256.3%</t>
+          <t>-273.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1471,22 +1471,22 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-159.4%</t>
+          <t>-170.0%</t>
         </is>
       </c>
     </row>
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.39868398140562</v>
+        <v>-12.53815648711955</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.793558456119</v>
+        <v>-1.849347458404573</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.727313387683918</v>
+        <v>-3.909001576609002</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9298835281466458</v>
+        <v>0.8208706147915952</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.17283882868621</v>
+        <v>-12.31231133440014</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.693641321995027</v>
+        <v>-1.7494303242806</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.685386712096754</v>
+        <v>-3.867074901021838</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.9646186065351525</v>
+        <v>0.8556056931801019</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.88656401636351</v>
+        <v>-12.02603652207745</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.57799225250989</v>
+        <v>-1.633781254795463</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.685386712096754</v>
+        <v>-3.867074901021838</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.9657577510912114</v>
+        <v>0.8567448377361608</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.9394593044078</v>
+        <v>-12.07893181012173</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.596516593565497</v>
+        <v>-1.65230559585107</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.680431366008308</v>
+        <v>-3.862119554933392</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.9713647329063866</v>
+        <v>0.8623518195513364</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.65555057347905</v>
+        <v>-11.79502307919299</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.477219396955361</v>
+        <v>-1.533008399240933</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.680431366008308</v>
+        <v>-3.862119554933392</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.9770984371450231</v>
+        <v>0.8680855237899729</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.4085633232861</v>
+        <v>-11.54803582900003</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.388161759272045</v>
+        <v>-1.443950761557618</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.61513230474044</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.115553524866929</v>
+        <v>1.006540611511879</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.14472645608203</v>
+        <v>-11.28419896179596</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.292510493703325</v>
+        <v>-1.348299495988898</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.61513230474044</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.105670043554022</v>
+        <v>0.9966571301989711</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.87748465521363</v>
+        <v>-11.01695716092757</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.187448333855339</v>
+        <v>-1.243237336140913</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.61513230474044</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.103835483054648</v>
+        <v>0.9948225696995974</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.60167549181315</v>
+        <v>-10.74114799752708</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.077424983468606</v>
+        <v>-1.13321398575418</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.344424807536623</v>
+        <v>-3.526112996461706</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.156946753048427</v>
+        <v>1.047933839693377</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.57772195083719</v>
+        <v>-10.71719445655112</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.067175060932729</v>
+        <v>-1.122964063218303</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.320471266560665</v>
+        <v>-3.502159455485749</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.171987383779495</v>
+        <v>1.062974470424445</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.31366201251439</v>
+        <v>-10.45313451822833</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9748114017653631</v>
+        <v>-1.030600404050936</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.056411328237869</v>
+        <v>-3.238099517162953</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.317163030611421</v>
+        <v>1.20815011725637</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.606582389009557</v>
+        <v>-9.746054894723489</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6947665860237291</v>
+        <v>-0.750555588309302</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.056411328237869</v>
+        <v>-3.238099517162953</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.31437599695112</v>
+        <v>1.20536308359607</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.566398090643366</v>
+        <v>-9.705870596357299</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6783492427894116</v>
+        <v>-0.7341382450749845</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.016227029871678</v>
+        <v>-3.197915218796762</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.338830199858676</v>
+        <v>1.229817286503625</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.486328295105562</v>
+        <v>-9.625800800819494</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6469545033535327</v>
+        <v>-0.7027435056391056</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.936157234333874</v>
+        <v>-3.117845423258958</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.386238898402115</v>
+        <v>1.277225985047065</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.252847072875962</v>
+        <v>-9.392319578589895</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5456375856238407</v>
+        <v>-0.6014265879094136</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.702676012104276</v>
+        <v>-2.88436420102936</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.534252060577727</v>
+        <v>1.425239147222676</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.073138542732089</v>
+        <v>-9.212611048446021</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4766463838792503</v>
+        <v>-0.5324353861648232</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.64550450794158</v>
+        <v>-2.827192696866664</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.565662752762385</v>
+        <v>1.456649839407335</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.940863069101201</v>
+        <v>-9.080335574815134</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4283687076798683</v>
+        <v>-0.4841577099654413</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.513229034310693</v>
+        <v>-2.694917223235777</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.640395523687944</v>
+        <v>1.531382610332894</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.750263394428048</v>
+        <v>-8.88973590014198</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3493137771229704</v>
+        <v>-0.4051027794085433</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.322629359637541</v>
+        <v>-2.504317548562625</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.757570389179472</v>
+        <v>1.648557475824422</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.501263595744467</v>
+        <v>-8.640736101458399</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2368075164258792</v>
+        <v>-0.2925965187114521</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.322629359637541</v>
+        <v>-2.504317548562625</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.770476730403131</v>
+        <v>1.66146381704808</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.606853585517571</v>
+        <v>-8.746326091231504</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4070194419343398</v>
+        <v>-0.4628084442199127</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.428219349410645</v>
+        <v>-2.609907538335729</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.579146806940049</v>
+        <v>1.470133893584999</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.625588487636168</v>
+        <v>-8.765060993350101</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3659690609046922</v>
+        <v>-0.4217580631902651</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.433815359070776</v>
+        <v>-2.609907538335729</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.624333543021057</v>
+        <v>1.518678235462086</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.348850312965356</v>
+        <v>-8.488322818679288</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2518947790503723</v>
+        <v>-0.3076837813359452</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.25199869796085</v>
+        <v>-2.428090877225803</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.736802551673007</v>
+        <v>1.631147244114036</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.221957906530285</v>
+        <v>-8.361430412244218</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2098518027298222</v>
+        <v>-0.2656408050153956</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.125106291525781</v>
+        <v>-2.301198470790733</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.804224009280571</v>
+        <v>1.698568701721599</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.178409499759594</v>
+        <v>-8.317882005473527</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1993930521166392</v>
+        <v>-0.2551820544022121</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.125106291525781</v>
+        <v>-2.301198470790733</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.797263397185478</v>
+        <v>1.691608089626506</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.936261106305736</v>
+        <v>-8.075733612019668</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.08807134035395281</v>
+        <v>-0.1438603426395257</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.125106291525781</v>
+        <v>-2.301198470790733</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.811725751566621</v>
+        <v>1.706070444007649</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.873031734537387</v>
+        <v>-8.012504240251321</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.06824747118741836</v>
+        <v>-0.1240364734729917</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.125106291525781</v>
+        <v>-2.301198470790733</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.806257872025816</v>
+        <v>1.700602564466844</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.686544042160381</v>
+        <v>-7.826016547874315</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.003845699773961098</v>
+        <v>-0.05194330251161228</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.938618599148774</v>
+        <v>-2.114710778413727</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.915648581462597</v>
+        <v>1.809993273903625</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.665394843256938</v>
+        <v>-7.804867348970872</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.02000635757266389</v>
+        <v>-0.03578264471290948</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.917469400245331</v>
+        <v>-2.093561579510284</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.936039079041988</v>
+        <v>1.830383771483016</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.421629401273494</v>
+        <v>-7.561101906987427</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1132932427130924</v>
+        <v>0.057504240427519</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.917469400245331</v>
+        <v>-2.093561579510284</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.931819787389039</v>
+        <v>1.826164479830067</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.157601334080233</v>
+        <v>-7.297073839794168</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2210287835104126</v>
+        <v>0.1652397812248387</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.715604001429377</v>
+        <v>-1.89169618069433</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.055063340598627</v>
+        <v>1.949408033039655</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.907750940131159</v>
+        <v>-7.047223445845093</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3137110160737446</v>
+        <v>0.2579220137881708</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.715604001429377</v>
+        <v>-1.89169618069433</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.047805415582329</v>
+        <v>1.942150108023357</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.60418345112718</v>
+        <v>-6.743655956841114</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4387371351959848</v>
+        <v>0.382948132910411</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.715604001429377</v>
+        <v>-1.89169618069433</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.051404539102978</v>
+        <v>1.945749231544006</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.530703542275166</v>
+        <v>-6.6701760479891</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4814566047913442</v>
+        <v>0.4256676025057704</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.642124092577363</v>
+        <v>-1.818216271842316</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.10881999046874</v>
+        <v>2.003164682909769</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.305670542606343</v>
+        <v>-6.445143048320277</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5704902822751703</v>
+        <v>0.5147012799895965</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.41709109290854</v>
+        <v>-1.593183272173493</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.242860267886331</v>
+        <v>2.137204960327359</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.091036164969936</v>
+        <v>-6.230508670683871</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6610388343840503</v>
+        <v>0.6052498320984765</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.202456715272133</v>
+        <v>-1.378548894537087</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.376335695522493</v>
+        <v>2.27068038796352</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.824435807995584</v>
+        <v>-5.963908313709519</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7488732359575865</v>
+        <v>0.6930842336720131</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.202456715272133</v>
+        <v>-1.378548894537087</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.357529954306288</v>
+        <v>2.251874646747316</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.584005311190724</v>
+        <v>-5.723477816904659</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8467885113044082</v>
+        <v>0.7909995090188344</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.962026218467273</v>
+        <v>-1.138118397732226</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.503531329014081</v>
+        <v>2.39787602145511</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.341214503541279</v>
+        <v>-5.480687009255213</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9478341481990067</v>
+        <v>0.8920451459134329</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.962026218467273</v>
+        <v>-1.138118397732226</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.507460642848902</v>
+        <v>2.40180533528993</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.10160941193419</v>
+        <v>-5.241081917648124</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.044354768759182</v>
+        <v>0.9885657664736085</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8949782707987785</v>
+        <v>-1.071070450063732</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.548367995367339</v>
+        <v>2.442712687808366</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.858953823511026</v>
+        <v>-4.99842632922496</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.138415075348441</v>
+        <v>1.082626073062867</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8949782707987785</v>
+        <v>-1.071070450063732</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.545366066587332</v>
+        <v>2.43971075902836</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.638933025474016</v>
+        <v>-4.77840553118795</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.228002431573859</v>
+        <v>1.172213429288286</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7537584257307982</v>
+        <v>-0.9298506049957516</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.631677010638734</v>
+        <v>2.526021703079762</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.439684395569206</v>
+        <v>-4.579156901283141</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.323596066337606</v>
+        <v>1.267807064052033</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7537584257307982</v>
+        <v>-0.9298506049957516</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.647571193440557</v>
+        <v>2.541915885881585</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.280169292049837</v>
+        <v>-4.419641797763771</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.388547952185656</v>
+        <v>1.332758949900082</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5942433222114283</v>
+        <v>-0.7703355014763816</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.744426099992481</v>
+        <v>2.63877079243351</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.135497146950099</v>
+        <v>-4.274969652664034</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.456504912786991</v>
+        <v>1.400715910501417</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4495711771116909</v>
+        <v>-0.6256633563766443</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.841317489613764</v>
+        <v>2.735662182054792</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.117727688019143</v>
+        <v>-4.257200193733078</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.378952388446095</v>
+        <v>1.323163386160521</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4318017181807353</v>
+        <v>-0.6078938974456887</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.767318857059059</v>
+        <v>2.661663549500087</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.030928190240134</v>
+        <v>-4.170400695954068</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.436072680880265</v>
+        <v>1.380283678594691</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4318017181807353</v>
+        <v>-0.6078938974456887</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.789719350381625</v>
+        <v>2.684064042822653</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.931235575511122</v>
+        <v>-4.070708081225057</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.476022128145282</v>
+        <v>1.420233125859708</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3321091034517236</v>
+        <v>-0.5082012827166769</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.849607320592444</v>
+        <v>2.743952013033472</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.736083384562804</v>
+        <v>3.389609180356691</v>
       </c>
       <c r="C1936" t="n">
         <v>3.05987970513818</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.999605761835132</v>
+        <v>-4.139078267549067</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.45968097609038</v>
+        <v>1.403891973804806</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3228334044155086</v>
+        <v>-0.4989255836804619</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.866179662488875</v>
+        <v>2.760524354929903</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240417.xlsx
+++ b/tame_output/ON/bt/strategyON_20240417.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>4.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-78.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.9%</t>
+          <t>119.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>98.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>780.5%</t>
+          <t>789.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-575.5%</t>
+          <t>-539.0%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-235.8%</t>
+          <t>-221.2%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-332.5%</t>
+          <t>-304.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.5%</t>
+          <t>-152.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-273.9%</t>
+          <t>-202.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-199.9%</t>
+          <t>-182.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-170.0%</t>
+          <t>-130.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1936"/>
+  <dimension ref="A1:G1937"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44130,10 +44130,10 @@
         <v>2.427104734297883</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5250283742467086</v>
+        <v>0.8074516836127928</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.425021591296339</v>
+        <v>3.59447557691599</v>
       </c>
     </row>
     <row r="1852">
@@ -44153,10 +44153,10 @@
         <v>2.316236135345659</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1970111525192294</v>
+        <v>0.4794344618853137</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.24854954799862</v>
+        <v>3.41800353361827</v>
       </c>
     </row>
     <row r="1853">
@@ -44176,10 +44176,10 @@
         <v>2.127004937140156</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.09202503827961067</v>
+        <v>0.374448347645695</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.193656629863417</v>
+        <v>3.363110615483068</v>
       </c>
     </row>
     <row r="1854">
@@ -44199,10 +44199,10 @@
         <v>1.93115731797425</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4003599897444861</v>
+        <v>-0.1179366803784018</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.899332005092691</v>
+        <v>3.068785990712342</v>
       </c>
     </row>
     <row r="1855">
@@ -44222,10 +44222,10 @@
         <v>1.775627700415084</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4003599897444861</v>
+        <v>-0.1179366803784018</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.897874543905555</v>
+        <v>3.067328529525205</v>
       </c>
     </row>
     <row r="1856">
@@ -44245,10 +44245,10 @@
         <v>1.639923714579035</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.5082660417717042</v>
+        <v>-0.22584273240562</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.83490003614384</v>
+        <v>3.00435402176349</v>
       </c>
     </row>
     <row r="1857">
@@ -44268,10 +44268,10 @@
         <v>1.492969633139954</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.8659163920100523</v>
+        <v>-0.5834930826439682</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.616415884657089</v>
+        <v>2.785869870276739</v>
       </c>
     </row>
     <row r="1858">
@@ -44291,10 +44291,10 @@
         <v>1.371048918641793</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.8659163920100523</v>
+        <v>-0.5834930826439682</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.618188811357348</v>
+        <v>2.787642796976999</v>
       </c>
     </row>
     <row r="1859">
@@ -44314,10 +44314,10 @@
         <v>1.184659488849283</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.002333888451319</v>
+        <v>-0.7199105790852351</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.522671200959993</v>
+        <v>2.692125186579643</v>
       </c>
     </row>
     <row r="1860">
@@ -44337,10 +44337,10 @@
         <v>1.042371252304275</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.084802138958467</v>
+        <v>-0.8023788295923833</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.461475025657794</v>
+        <v>2.630929011277445</v>
       </c>
     </row>
     <row r="1861">
@@ -44360,10 +44360,10 @@
         <v>0.9066867850680596</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.084802138958467</v>
+        <v>-0.8023788295923833</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.460055617313759</v>
+        <v>2.62950960293341</v>
       </c>
     </row>
     <row r="1862">
@@ -44383,10 +44383,10 @@
         <v>0.7677238473421761</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.183023775825593</v>
+        <v>-0.9006004664595091</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.407610195427726</v>
+        <v>2.577064181047376</v>
       </c>
     </row>
     <row r="1863">
@@ -44406,10 +44406,10 @@
         <v>0.6209274092925088</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.479334560124606</v>
+        <v>-1.196911250758522</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.229078239854149</v>
+        <v>2.3985322254738</v>
       </c>
     </row>
     <row r="1864">
@@ -44429,10 +44429,10 @@
         <v>0.4562534424349964</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.6055000279392</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.982686517560501</v>
+        <v>2.152140503180152</v>
       </c>
     </row>
     <row r="1865">
@@ -44452,10 +44452,10 @@
         <v>0.2862458812500197</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.6055000279392</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.977871950031962</v>
+        <v>2.147325935651613</v>
       </c>
     </row>
     <row r="1866">
@@ -44475,10 +44475,10 @@
         <v>0.117683182144098</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.6055000279392</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.975866000640839</v>
+        <v>2.14531998626049</v>
       </c>
     </row>
     <row r="1867">
@@ -44498,10 +44498,10 @@
         <v>-0.02272893139916077</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.6055000279392</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.986124691309518</v>
+        <v>2.155578676929169</v>
       </c>
     </row>
     <row r="1868">
@@ -44521,10 +44521,10 @@
         <v>-0.164979295047389</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.6055000279392</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.982224256455214</v>
+        <v>2.151678242074864</v>
       </c>
     </row>
     <row r="1869">
@@ -44544,10 +44544,10 @@
         <v>-0.2917042946903794</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.6055000279392</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.980629176510215</v>
+        <v>2.150083162129865</v>
       </c>
     </row>
     <row r="1870">
@@ -44567,10 +44567,10 @@
         <v>-0.4065898554852505</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.956666473039163</v>
+        <v>-1.674243163673079</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.943162270999096</v>
+        <v>2.112616256618746</v>
       </c>
     </row>
     <row r="1871">
@@ -44590,10 +44590,10 @@
         <v>-0.583955803263748</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.956666473039163</v>
+        <v>-1.674243163673079</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.939135966464693</v>
+        <v>2.108589952084343</v>
       </c>
     </row>
     <row r="1872">
@@ -44613,10 +44613,10 @@
         <v>-0.7372584600823844</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.956666473039163</v>
+        <v>-1.674243163673079</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.939033865143108</v>
+        <v>2.108487850762759</v>
       </c>
     </row>
     <row r="1873">
@@ -44636,10 +44636,10 @@
         <v>-0.8846810745794653</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.33165179921044</v>
+        <v>-2.049228489844356</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.716614185411772</v>
+        <v>1.886068171031423</v>
       </c>
     </row>
     <row r="1874">
@@ -44659,10 +44659,10 @@
         <v>-1.023142900283015</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.33165179921044</v>
+        <v>-2.049228489844356</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.721964488709822</v>
+        <v>1.891418474329473</v>
       </c>
     </row>
     <row r="1875">
@@ -44682,10 +44682,10 @@
         <v>-1.145786891791844</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.658051827875453</v>
+        <v>-2.375628518509369</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.534040491467992</v>
+        <v>1.703494477087643</v>
       </c>
     </row>
     <row r="1876">
@@ -44705,10 +44705,10 @@
         <v>-1.230404728399753</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.877200795949651</v>
+        <v>-2.594777486583566</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.405592861245242</v>
+        <v>1.575046846864893</v>
       </c>
     </row>
     <row r="1877">
@@ -44728,10 +44728,10 @@
         <v>-1.22892835841719</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.877200795949651</v>
+        <v>-2.594777486583566</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.405592861245242</v>
+        <v>1.575046846864893</v>
       </c>
     </row>
     <row r="1878">
@@ -44751,10 +44751,10 @@
         <v>-1.305118431430492</v>
       </c>
       <c r="F1878" t="n">
-        <v>-3.00483974056364</v>
+        <v>-2.722416431197555</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.334522691595491</v>
+        <v>1.503976677215142</v>
       </c>
     </row>
     <row r="1879">
@@ -44774,10 +44774,10 @@
         <v>-1.387850985598527</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.179610508659539</v>
+        <v>-2.897187199293454</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.234142785222388</v>
+        <v>1.403596770842038</v>
       </c>
     </row>
     <row r="1880">
@@ -44797,10 +44797,10 @@
         <v>-1.343091351438127</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.10614067699209</v>
+        <v>-2.823717367626006</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.293596385716278</v>
+        <v>1.463050371335929</v>
       </c>
     </row>
     <row r="1881">
@@ -44820,10 +44820,10 @@
         <v>-1.398585897645227</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.281265094378634</v>
+        <v>-2.99884178501255</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.203076956031869</v>
+        <v>1.372530941651519</v>
       </c>
     </row>
     <row r="1882">
@@ -44843,10 +44843,10 @@
         <v>-1.499585900152619</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.281265094378634</v>
+        <v>-2.99884178501255</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.195857791130273</v>
+        <v>1.365311776749923</v>
       </c>
     </row>
     <row r="1883">
@@ -44866,10 +44866,10 @@
         <v>-1.621379628741491</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.569068938915872</v>
+        <v>-3.286645629549788</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.016503293633954</v>
+        <v>1.185957279253604</v>
       </c>
     </row>
     <row r="1884">
@@ -44889,10 +44889,10 @@
         <v>-1.712193617768464</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.731716475986033</v>
+        <v>-3.449293166619948</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9200305612304134</v>
+        <v>1.089484546850064</v>
       </c>
     </row>
     <row r="1885">
@@ -44912,10 +44912,10 @@
         <v>-1.802311457033854</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.793729173174456</v>
+        <v>-3.511305863808372</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.8855166715464744</v>
+        <v>1.054970657166125</v>
       </c>
     </row>
     <row r="1886">
@@ -44935,10 +44935,10 @@
         <v>-1.777514915759928</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.793729173174456</v>
+        <v>-3.511305863808372</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.8895070072328752</v>
+        <v>1.058960992852526</v>
       </c>
     </row>
     <row r="1887">
@@ -44958,10 +44958,10 @@
         <v>-1.835658879348318</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.793729173174456</v>
+        <v>-3.511305863808372</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.8880317803341335</v>
+        <v>1.057485765953784</v>
       </c>
     </row>
     <row r="1888">
@@ -44981,10 +44981,10 @@
         <v>-1.860168165367156</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.892635913633731</v>
+        <v>-3.610212604267647</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8437411462234405</v>
+        <v>1.013195131843091</v>
       </c>
     </row>
     <row r="1889">
@@ -45004,10 +45004,10 @@
         <v>-1.849347458404573</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.909001576609002</v>
+        <v>-3.626578267242917</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.8208706147915952</v>
+        <v>0.9903246004112458</v>
       </c>
     </row>
     <row r="1890">
@@ -45027,10 +45027,10 @@
         <v>-1.7494303242806</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.867074901021838</v>
+        <v>-3.584651591655754</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.8556056931801019</v>
+        <v>1.025059678799753</v>
       </c>
     </row>
     <row r="1891">
@@ -45050,10 +45050,10 @@
         <v>-1.633781254795463</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.867074901021838</v>
+        <v>-3.584651591655754</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.8567448377361608</v>
+        <v>1.026198823355811</v>
       </c>
     </row>
     <row r="1892">
@@ -45073,10 +45073,10 @@
         <v>-1.65230559585107</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.862119554933392</v>
+        <v>-3.579696245567308</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.8623518195513364</v>
+        <v>1.031805805170987</v>
       </c>
     </row>
     <row r="1893">
@@ -45096,10 +45096,10 @@
         <v>-1.533008399240933</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.862119554933392</v>
+        <v>-3.579696245567308</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.8680855237899729</v>
+        <v>1.037539509409624</v>
       </c>
     </row>
     <row r="1894">
@@ -45119,10 +45119,10 @@
         <v>-1.443950761557618</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.61513230474044</v>
+        <v>-3.332708995374356</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.006540611511879</v>
+        <v>1.17599459713153</v>
       </c>
     </row>
     <row r="1895">
@@ -45142,10 +45142,10 @@
         <v>-1.348299495988898</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.61513230474044</v>
+        <v>-3.332708995374356</v>
       </c>
       <c r="G1895" t="n">
-        <v>0.9966571301989711</v>
+        <v>1.166111115818622</v>
       </c>
     </row>
     <row r="1896">
@@ -45165,10 +45165,10 @@
         <v>-1.243237336140913</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.61513230474044</v>
+        <v>-3.332708995374356</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.9948225696995974</v>
+        <v>1.164276555319248</v>
       </c>
     </row>
     <row r="1897">
@@ -45188,10 +45188,10 @@
         <v>-1.13321398575418</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.526112996461706</v>
+        <v>-3.243689687095622</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.047933839693377</v>
+        <v>1.217387825313027</v>
       </c>
     </row>
     <row r="1898">
@@ -45211,10 +45211,10 @@
         <v>-1.122964063218303</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.502159455485749</v>
+        <v>-3.219736146119665</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.062974470424445</v>
+        <v>1.232428456044096</v>
       </c>
     </row>
     <row r="1899">
@@ -45234,10 +45234,10 @@
         <v>-1.030600404050936</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.238099517162953</v>
+        <v>-2.955676207796869</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.20815011725637</v>
+        <v>1.377604102876021</v>
       </c>
     </row>
     <row r="1900">
@@ -45257,10 +45257,10 @@
         <v>-0.750555588309302</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.238099517162953</v>
+        <v>-2.955676207796869</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.20536308359607</v>
+        <v>1.37481706921572</v>
       </c>
     </row>
     <row r="1901">
@@ -45280,10 +45280,10 @@
         <v>-0.7341382450749845</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.197915218796762</v>
+        <v>-2.915491909430678</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.229817286503625</v>
+        <v>1.399271272123276</v>
       </c>
     </row>
     <row r="1902">
@@ -45303,10 +45303,10 @@
         <v>-0.7027435056391056</v>
       </c>
       <c r="F1902" t="n">
-        <v>-3.117845423258958</v>
+        <v>-2.835422113892874</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.277225985047065</v>
+        <v>1.446679970666715</v>
       </c>
     </row>
     <row r="1903">
@@ -45326,10 +45326,10 @@
         <v>-0.6014265879094136</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.88436420102936</v>
+        <v>-2.601940891663275</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.425239147222676</v>
+        <v>1.594693132842327</v>
       </c>
     </row>
     <row r="1904">
@@ -45349,10 +45349,10 @@
         <v>-0.5324353861648232</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.827192696866664</v>
+        <v>-2.544769387500579</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.456649839407335</v>
+        <v>1.626103825026985</v>
       </c>
     </row>
     <row r="1905">
@@ -45372,10 +45372,10 @@
         <v>-0.4841577099654413</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.694917223235777</v>
+        <v>-2.412493913869693</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.531382610332894</v>
+        <v>1.700836595952544</v>
       </c>
     </row>
     <row r="1906">
@@ -45395,10 +45395,10 @@
         <v>-0.4051027794085433</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.504317548562625</v>
+        <v>-2.22189423919654</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.648557475824422</v>
+        <v>1.818011461444072</v>
       </c>
     </row>
     <row r="1907">
@@ -45418,10 +45418,10 @@
         <v>-0.2925965187114521</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.504317548562625</v>
+        <v>-2.22189423919654</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.66146381704808</v>
+        <v>1.830917802667731</v>
       </c>
     </row>
     <row r="1908">
@@ -45441,10 +45441,10 @@
         <v>-0.4628084442199127</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.609907538335729</v>
+        <v>-2.327484228969645</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.470133893584999</v>
+        <v>1.63958787920465</v>
       </c>
     </row>
     <row r="1909">
@@ -45464,10 +45464,10 @@
         <v>-0.4217580631902651</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.609907538335729</v>
+        <v>-2.333080238629776</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.518678235462086</v>
+        <v>1.684774615285658</v>
       </c>
     </row>
     <row r="1910">
@@ -45487,10 +45487,10 @@
         <v>-0.3076837813359452</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.428090877225803</v>
+        <v>-2.15126357751985</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.631147244114036</v>
+        <v>1.797243623937608</v>
       </c>
     </row>
     <row r="1911">
@@ -45510,10 +45510,10 @@
         <v>-0.2656408050153956</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.301198470790733</v>
+        <v>-2.02437117108478</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.698568701721599</v>
+        <v>1.864665081545171</v>
       </c>
     </row>
     <row r="1912">
@@ -45533,10 +45533,10 @@
         <v>-0.2551820544022121</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.301198470790733</v>
+        <v>-2.02437117108478</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.691608089626506</v>
+        <v>1.857704469450078</v>
       </c>
     </row>
     <row r="1913">
@@ -45556,10 +45556,10 @@
         <v>-0.1438603426395257</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.301198470790733</v>
+        <v>-2.02437117108478</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.706070444007649</v>
+        <v>1.872166823831221</v>
       </c>
     </row>
     <row r="1914">
@@ -45579,10 +45579,10 @@
         <v>-0.1240364734729917</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.301198470790733</v>
+        <v>-2.02437117108478</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.700602564466844</v>
+        <v>1.866698944290416</v>
       </c>
     </row>
     <row r="1915">
@@ -45602,10 +45602,10 @@
         <v>-0.05194330251161228</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.114710778413727</v>
+        <v>-1.837883478707774</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.809993273903625</v>
+        <v>1.976089653727197</v>
       </c>
     </row>
     <row r="1916">
@@ -45625,10 +45625,10 @@
         <v>-0.03578264471290948</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.093561579510284</v>
+        <v>-1.81673427980433</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.830383771483016</v>
+        <v>1.996480151306589</v>
       </c>
     </row>
     <row r="1917">
@@ -45648,10 +45648,10 @@
         <v>0.057504240427519</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.093561579510284</v>
+        <v>-1.81673427980433</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.826164479830067</v>
+        <v>1.992260859653639</v>
       </c>
     </row>
     <row r="1918">
@@ -45671,10 +45671,10 @@
         <v>0.1652397812248387</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.89169618069433</v>
+        <v>-1.614868880988377</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.949408033039655</v>
+        <v>2.115504412863228</v>
       </c>
     </row>
     <row r="1919">
@@ -45694,10 +45694,10 @@
         <v>0.2579220137881708</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.89169618069433</v>
+        <v>-1.614868880988377</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.942150108023357</v>
+        <v>2.108246487846929</v>
       </c>
     </row>
     <row r="1920">
@@ -45717,10 +45717,10 @@
         <v>0.382948132910411</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.89169618069433</v>
+        <v>-1.614868880988377</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.945749231544006</v>
+        <v>2.111845611367579</v>
       </c>
     </row>
     <row r="1921">
@@ -45740,10 +45740,10 @@
         <v>0.4256676025057704</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.818216271842316</v>
+        <v>-1.541388972136363</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.003164682909769</v>
+        <v>2.169261062733341</v>
       </c>
     </row>
     <row r="1922">
@@ -45763,10 +45763,10 @@
         <v>0.5147012799895965</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.593183272173493</v>
+        <v>-1.31635597246754</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.137204960327359</v>
+        <v>2.303301340150931</v>
       </c>
     </row>
     <row r="1923">
@@ -45786,10 +45786,10 @@
         <v>0.6052498320984765</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.378548894537087</v>
+        <v>-1.101721594831133</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.27068038796352</v>
+        <v>2.436776767787093</v>
       </c>
     </row>
     <row r="1924">
@@ -45809,10 +45809,10 @@
         <v>0.6930842336720131</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.378548894537087</v>
+        <v>-1.101721594831133</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.251874646747316</v>
+        <v>2.417971026570888</v>
       </c>
     </row>
     <row r="1925">
@@ -45832,10 +45832,10 @@
         <v>0.7909995090188344</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.138118397732226</v>
+        <v>-0.8612910980262725</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.39787602145511</v>
+        <v>2.563972401278682</v>
       </c>
     </row>
     <row r="1926">
@@ -45855,10 +45855,10 @@
         <v>0.8920451459134329</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.138118397732226</v>
+        <v>-0.8612910980262725</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.40180533528993</v>
+        <v>2.567901715113502</v>
       </c>
     </row>
     <row r="1927">
@@ -45878,10 +45878,10 @@
         <v>0.9885657664736085</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.071070450063732</v>
+        <v>-0.7942431503577779</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.442712687808366</v>
+        <v>2.608809067631939</v>
       </c>
     </row>
     <row r="1928">
@@ -45901,10 +45901,10 @@
         <v>1.082626073062867</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.071070450063732</v>
+        <v>-0.7942431503577779</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.43971075902836</v>
+        <v>2.605807138851932</v>
       </c>
     </row>
     <row r="1929">
@@ -45924,10 +45924,10 @@
         <v>1.172213429288286</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.9298506049957516</v>
+        <v>-0.6530233052897977</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.526021703079762</v>
+        <v>2.692118082903335</v>
       </c>
     </row>
     <row r="1930">
@@ -45947,10 +45947,10 @@
         <v>1.267807064052033</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.9298506049957516</v>
+        <v>-0.6530233052897977</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.541915885881585</v>
+        <v>2.708012265705158</v>
       </c>
     </row>
     <row r="1931">
@@ -45970,10 +45970,10 @@
         <v>1.332758949900082</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7703355014763816</v>
+        <v>-0.4935082017704278</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.63877079243351</v>
+        <v>2.804867172257082</v>
       </c>
     </row>
     <row r="1932">
@@ -45993,10 +45993,10 @@
         <v>1.400715910501417</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6256633563766443</v>
+        <v>-0.3488360566706903</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.735662182054792</v>
+        <v>2.901758561878364</v>
       </c>
     </row>
     <row r="1933">
@@ -46016,10 +46016,10 @@
         <v>1.323163386160521</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6078938974456887</v>
+        <v>-0.3310665977397348</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.661663549500087</v>
+        <v>2.827759929323659</v>
       </c>
     </row>
     <row r="1934">
@@ -46039,10 +46039,10 @@
         <v>1.380283678594691</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6078938974456887</v>
+        <v>-0.3310665977397348</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.684064042822653</v>
+        <v>2.850160422646225</v>
       </c>
     </row>
     <row r="1935">
@@ -46062,10 +46062,10 @@
         <v>1.420233125859708</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5082012827166769</v>
+        <v>-0.231373983010723</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.743952013033472</v>
+        <v>2.910048392857044</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,45 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.389609180356691</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.05987970513818</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.139078267549067</v>
+        <v>-3.773780022203414</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.403891973804806</v>
+        <v>1.550011271943067</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4989255836804619</v>
+        <v>0.2108353359733297</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.760524354929903</v>
+        <v>3.186380906722178</v>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" s="2" t="n">
+        <v>45399</v>
+      </c>
+      <c r="B1937" t="n">
+        <v>3.736182382997127</v>
+      </c>
+      <c r="C1937" t="n">
+        <v>3.161299661277118</v>
+      </c>
+      <c r="D1937" t="n">
+        <v>-3.773780022203414</v>
+      </c>
+      <c r="E1937" t="n">
+        <v>1.550011271943067</v>
+      </c>
+      <c r="F1937" t="n">
+        <v>0.2108353359733297</v>
+      </c>
+      <c r="G1937" t="n">
+        <v>3.154363458263486</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240417.xlsx
+++ b/tame_output/ON/bt/strategyON_20240417.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -661,17 +661,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>8.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,25 +811,25 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>-23.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.7%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119.5%</t>
+          <t>118.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-736.4%</t>
+          <t>-722.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.9%</t>
+          <t>-58.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>789.1%</t>
+          <t>780.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-539.0%</t>
+          <t>-561.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-289.2%</t>
+          <t>-283.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-46.1%</t>
+          <t>-45.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-101.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-221.2%</t>
+          <t>-230.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-30.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,15 +1285,15 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-304.2%</t>
+          <t>-332.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-39.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-152.1%</t>
+          <t>-160.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-202.9%</t>
+          <t>-255.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,15 +1443,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-182.9%</t>
+          <t>-199.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-130.6%</t>
+          <t>-158.8%</t>
         </is>
       </c>
     </row>
@@ -44130,10 +44130,10 @@
         <v>2.427104734297883</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.8074516836127928</v>
+        <v>0.5250283742467086</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.59447557691599</v>
+        <v>3.425021591296339</v>
       </c>
     </row>
     <row r="1852">
@@ -44153,10 +44153,10 @@
         <v>2.316236135345659</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4794344618853137</v>
+        <v>0.1970111525192294</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.41800353361827</v>
+        <v>3.24854954799862</v>
       </c>
     </row>
     <row r="1853">
@@ -44176,10 +44176,10 @@
         <v>2.127004937140156</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.374448347645695</v>
+        <v>0.09202503827961067</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.363110615483068</v>
+        <v>3.193656629863417</v>
       </c>
     </row>
     <row r="1854">
@@ -44199,10 +44199,10 @@
         <v>1.93115731797425</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1179366803784018</v>
+        <v>-0.4003599897444861</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.068785990712342</v>
+        <v>2.899332005092691</v>
       </c>
     </row>
     <row r="1855">
@@ -44222,10 +44222,10 @@
         <v>1.775627700415084</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1179366803784018</v>
+        <v>-0.4003599897444861</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.067328529525205</v>
+        <v>2.897874543905555</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44245,10 +44245,10 @@
         <v>1.639923714579035</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.22584273240562</v>
+        <v>-0.5082660417717042</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.00435402176349</v>
+        <v>2.83490003614384</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44268,10 +44268,10 @@
         <v>1.492969633139954</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.5834930826439682</v>
+        <v>-0.8659163920100523</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.785869870276739</v>
+        <v>2.616415884657089</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44291,10 +44291,10 @@
         <v>1.371048918641793</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.5834930826439682</v>
+        <v>-0.8659163920100523</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.787642796976999</v>
+        <v>2.618188811357348</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44314,10 +44314,10 @@
         <v>1.184659488849283</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.7199105790852351</v>
+        <v>-1.002333888451319</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.692125186579643</v>
+        <v>2.522671200959993</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44337,10 +44337,10 @@
         <v>1.042371252304275</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8023788295923833</v>
+        <v>-1.084802138958467</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.630929011277445</v>
+        <v>2.461475025657794</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44360,10 +44360,10 @@
         <v>0.9066867850680596</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8023788295923833</v>
+        <v>-1.084802138958467</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.62950960293341</v>
+        <v>2.460055617313759</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44383,10 +44383,10 @@
         <v>0.7677238473421761</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9006004664595091</v>
+        <v>-1.183023775825593</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.577064181047376</v>
+        <v>2.407610195427726</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44406,10 +44406,10 @@
         <v>0.6209274092925088</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.196911250758522</v>
+        <v>-1.479334560124606</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.3985322254738</v>
+        <v>2.229078239854149</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44429,10 +44429,10 @@
         <v>0.4562534424349964</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.6055000279392</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.152140503180152</v>
+        <v>1.982686517560501</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44452,10 +44452,10 @@
         <v>0.2862458812500197</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.6055000279392</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.147325935651613</v>
+        <v>1.977871950031962</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44475,10 +44475,10 @@
         <v>0.117683182144098</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.6055000279392</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.14531998626049</v>
+        <v>1.975866000640839</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44498,10 +44498,10 @@
         <v>-0.02272893139916077</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.6055000279392</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.155578676929169</v>
+        <v>1.986124691309518</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44521,10 +44521,10 @@
         <v>-0.164979295047389</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.6055000279392</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.151678242074864</v>
+        <v>1.982224256455214</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44544,10 +44544,10 @@
         <v>-0.2917042946903794</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.6055000279392</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.150083162129865</v>
+        <v>1.980629176510215</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44567,10 +44567,10 @@
         <v>-0.4065898554852505</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.674243163673079</v>
+        <v>-1.956666473039163</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.112616256618746</v>
+        <v>1.943162270999096</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44590,10 +44590,10 @@
         <v>-0.583955803263748</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.674243163673079</v>
+        <v>-1.956666473039163</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.108589952084343</v>
+        <v>1.939135966464693</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44613,10 +44613,10 @@
         <v>-0.7372584600823844</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.674243163673079</v>
+        <v>-1.956666473039163</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.108487850762759</v>
+        <v>1.939033865143108</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44636,10 +44636,10 @@
         <v>-0.8846810745794653</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.049228489844356</v>
+        <v>-2.33165179921044</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.886068171031423</v>
+        <v>1.716614185411772</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44659,10 +44659,10 @@
         <v>-1.023142900283015</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.049228489844356</v>
+        <v>-2.33165179921044</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.891418474329473</v>
+        <v>1.721964488709822</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44682,10 +44682,10 @@
         <v>-1.145786891791844</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.375628518509369</v>
+        <v>-2.658051827875453</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.703494477087643</v>
+        <v>1.534040491467992</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44705,10 +44705,10 @@
         <v>-1.230404728399753</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.594777486583566</v>
+        <v>-2.877200795949651</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.575046846864893</v>
+        <v>1.405592861245242</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44728,10 +44728,10 @@
         <v>-1.22892835841719</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.594777486583566</v>
+        <v>-2.877200795949651</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.575046846864893</v>
+        <v>1.405592861245242</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44751,10 +44751,10 @@
         <v>-1.305118431430492</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.722416431197555</v>
+        <v>-3.00483974056364</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.503976677215142</v>
+        <v>1.334522691595491</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44774,10 +44774,10 @@
         <v>-1.387850985598527</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.897187199293454</v>
+        <v>-3.179610508659539</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.403596770842038</v>
+        <v>1.234142785222388</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44797,10 +44797,10 @@
         <v>-1.343091351438127</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.823717367626006</v>
+        <v>-3.10614067699209</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.463050371335929</v>
+        <v>1.293596385716278</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078594</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44820,10 +44820,10 @@
         <v>-1.398585897645227</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.99884178501255</v>
+        <v>-3.281265094378634</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.372530941651519</v>
+        <v>1.203076956031869</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880266</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44843,10 +44843,10 @@
         <v>-1.499585900152619</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.99884178501255</v>
+        <v>-3.281265094378634</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.365311776749923</v>
+        <v>1.195857791130273</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234391</v>
+        <v>3.48068891723439</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44866,10 +44866,10 @@
         <v>-1.621379628741491</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.286645629549788</v>
+        <v>-3.569068938915872</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.185957279253604</v>
+        <v>1.016503293633954</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860581</v>
+        <v>3.49371243886058</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44889,10 +44889,10 @@
         <v>-1.712193617768464</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.449293166619948</v>
+        <v>-3.731716475986033</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.089484546850064</v>
+        <v>0.9200305612304134</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44912,10 +44912,10 @@
         <v>-1.802311457033854</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.511305863808372</v>
+        <v>-3.793729173174456</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.054970657166125</v>
+        <v>0.8855166715464744</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44935,10 +44935,10 @@
         <v>-1.777514915759928</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.511305863808372</v>
+        <v>-3.793729173174456</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.058960992852526</v>
+        <v>0.8895070072328752</v>
       </c>
     </row>
     <row r="1887">
@@ -44958,10 +44958,10 @@
         <v>-1.835658879348318</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.511305863808372</v>
+        <v>-3.793729173174456</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.057485765953784</v>
+        <v>0.8880317803341335</v>
       </c>
     </row>
     <row r="1888">
@@ -44981,10 +44981,10 @@
         <v>-1.860168165367156</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.610212604267647</v>
+        <v>-3.892635913633731</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.013195131843091</v>
+        <v>0.8437411462234405</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.53815648711955</v>
+        <v>-12.39868398140562</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.849347458404573</v>
+        <v>-1.793558456119</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.626578267242917</v>
+        <v>-3.727313387683918</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9903246004112458</v>
+        <v>0.9298835281466458</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.31231133440014</v>
+        <v>-12.17283882868621</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.7494303242806</v>
+        <v>-1.693641321995027</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.584651591655754</v>
+        <v>-3.685386712096754</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.025059678799753</v>
+        <v>0.9646186065351525</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-12.02603652207745</v>
+        <v>-11.88656401636351</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.633781254795463</v>
+        <v>-1.57799225250989</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.584651591655754</v>
+        <v>-3.685386712096754</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.026198823355811</v>
+        <v>0.9657577510912114</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-12.07893181012173</v>
+        <v>-11.9394593044078</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.65230559585107</v>
+        <v>-1.596516593565497</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.579696245567308</v>
+        <v>-3.680431366008308</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.031805805170987</v>
+        <v>0.9713647329063866</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.79502307919299</v>
+        <v>-11.65555057347905</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.533008399240933</v>
+        <v>-1.477219396955361</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.579696245567308</v>
+        <v>-3.680431366008308</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.037539509409624</v>
+        <v>0.9770984371450231</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.54803582900003</v>
+        <v>-11.4085633232861</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.443950761557618</v>
+        <v>-1.388161759272045</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.332708995374356</v>
+        <v>-3.433444115815356</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.17599459713153</v>
+        <v>1.115553524866929</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.28419896179596</v>
+        <v>-11.14472645608203</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.348299495988898</v>
+        <v>-1.292510493703325</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.332708995374356</v>
+        <v>-3.433444115815356</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.166111115818622</v>
+        <v>1.105670043554022</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-11.01695716092757</v>
+        <v>-10.87748465521363</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.243237336140913</v>
+        <v>-1.187448333855339</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.332708995374356</v>
+        <v>-3.433444115815356</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.164276555319248</v>
+        <v>1.103835483054648</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.74114799752708</v>
+        <v>-10.60167549181315</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.13321398575418</v>
+        <v>-1.077424983468606</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.243689687095622</v>
+        <v>-3.344424807536623</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.217387825313027</v>
+        <v>1.156946753048427</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.71719445655112</v>
+        <v>-10.57772195083719</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.122964063218303</v>
+        <v>-1.067175060932729</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.219736146119665</v>
+        <v>-3.320471266560665</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.232428456044096</v>
+        <v>1.171987383779495</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.45313451822833</v>
+        <v>-10.31366201251439</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.030600404050936</v>
+        <v>-0.9748114017653631</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.955676207796869</v>
+        <v>-3.056411328237869</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.377604102876021</v>
+        <v>1.317163030611421</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.746054894723489</v>
+        <v>-9.606582389009557</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.750555588309302</v>
+        <v>-0.6947665860237291</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.955676207796869</v>
+        <v>-3.056411328237869</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.37481706921572</v>
+        <v>1.31437599695112</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.839370871858726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.705870596357299</v>
+        <v>-9.566398090643366</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7341382450749845</v>
+        <v>-0.6783492427894116</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.915491909430678</v>
+        <v>-3.016227029871678</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.399271272123276</v>
+        <v>1.338830199858676</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.625800800819494</v>
+        <v>-9.486328295105562</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7027435056391056</v>
+        <v>-0.6469545033535327</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.835422113892874</v>
+        <v>-2.936157234333874</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.446679970666715</v>
+        <v>1.386238898402115</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.392319578589895</v>
+        <v>-9.252847072875962</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6014265879094136</v>
+        <v>-0.5456375856238407</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.601940891663275</v>
+        <v>-2.702676012104276</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.594693132842327</v>
+        <v>1.534252060577727</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.212611048446021</v>
+        <v>-9.073138542732089</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5324353861648232</v>
+        <v>-0.4766463838792503</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.544769387500579</v>
+        <v>-2.64550450794158</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.626103825026985</v>
+        <v>1.565662752762385</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.080335574815134</v>
+        <v>-8.940863069101201</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4841577099654413</v>
+        <v>-0.4283687076798683</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.412493913869693</v>
+        <v>-2.513229034310693</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.700836595952544</v>
+        <v>1.640395523687944</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.88973590014198</v>
+        <v>-8.750263394428048</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4051027794085433</v>
+        <v>-0.3493137771229704</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.22189423919654</v>
+        <v>-2.322629359637541</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.818011461444072</v>
+        <v>1.757570389179472</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.640736101458399</v>
+        <v>-8.501263595744467</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2925965187114521</v>
+        <v>-0.2368075164258792</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.22189423919654</v>
+        <v>-2.322629359637541</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.830917802667731</v>
+        <v>1.770476730403131</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.746326091231504</v>
+        <v>-8.606853585517571</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4628084442199127</v>
+        <v>-0.4070194419343398</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.327484228969645</v>
+        <v>-2.428219349410645</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.63958787920465</v>
+        <v>1.579146806940049</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.765060993350101</v>
+        <v>-8.480844023348592</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4217580631902651</v>
+        <v>-0.3080712751896613</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.333080238629776</v>
+        <v>-2.428219349410645</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.684774615285658</v>
+        <v>1.627691148817136</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.488322818679288</v>
+        <v>-8.204105848677779</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3076837813359452</v>
+        <v>-0.1939969933353418</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.15126357751985</v>
+        <v>-2.246402688300719</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.797243623937608</v>
+        <v>1.740160157469086</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.361430412244218</v>
+        <v>-8.077213442242709</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2656408050153956</v>
+        <v>-0.1519540170147917</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.02437117108478</v>
+        <v>-2.119510281865649</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.864665081545171</v>
+        <v>1.80758161507665</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.317882005473527</v>
+        <v>-8.033665035472017</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2551820544022121</v>
+        <v>-0.1414952664016083</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.02437117108478</v>
+        <v>-2.119510281865649</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.857704469450078</v>
+        <v>1.800621002981557</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.075733612019668</v>
+        <v>-7.791516642018159</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1438603426395257</v>
+        <v>-0.03017355463892191</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.02437117108478</v>
+        <v>-2.119510281865649</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.872166823831221</v>
+        <v>1.8150833573627</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.012504240251321</v>
+        <v>-7.728287270249811</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1240364734729917</v>
+        <v>-0.01034968547238746</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.02437117108478</v>
+        <v>-2.119510281865649</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.866698944290416</v>
+        <v>1.809615477821895</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.826016547874315</v>
+        <v>-7.541799577872805</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.05194330251161228</v>
+        <v>0.06174348548899156</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.837883478707774</v>
+        <v>-1.933022589488643</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.976089653727197</v>
+        <v>1.919006187258675</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.804867348970872</v>
+        <v>-7.520650378969362</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.03578264471290948</v>
+        <v>0.07790414328769479</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.81673427980433</v>
+        <v>-1.9118733905852</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.996480151306589</v>
+        <v>1.939396684838067</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.561101906987427</v>
+        <v>-7.276884936985917</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.057504240427519</v>
+        <v>0.1711910284281228</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.81673427980433</v>
+        <v>-1.9118733905852</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.992260859653639</v>
+        <v>1.935177393185118</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.297073839794168</v>
+        <v>-7.012856869792657</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1652397812248387</v>
+        <v>0.278926569225443</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.614868880988377</v>
+        <v>-1.710007991769246</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.115504412863228</v>
+        <v>2.058420946394706</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.047223445845093</v>
+        <v>-6.763006475843582</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2579220137881708</v>
+        <v>0.3716088017887751</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.614868880988377</v>
+        <v>-1.710007991769246</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.108246487846929</v>
+        <v>2.051163021378408</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.743655956841114</v>
+        <v>-6.603393035819901</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.382948132910411</v>
+        <v>0.4390533013188964</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.614868880988377</v>
+        <v>-1.710007991769246</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.111845611367579</v>
+        <v>2.054762144899057</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862983</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.6701760479891</v>
+        <v>-6.529913126967887</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4256676025057704</v>
+        <v>0.4817727709142554</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.541388972136363</v>
+        <v>-1.636528082917232</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.169261062733341</v>
+        <v>2.112177596264819</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102778</v>
+        <v>3.773761647102776</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.445143048320277</v>
+        <v>-6.304880127299064</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5147012799895965</v>
+        <v>0.5708064483980815</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.31635597246754</v>
+        <v>-1.411495083248409</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.303301340150931</v>
+        <v>2.24621787368241</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.230508670683871</v>
+        <v>-6.090245749662658</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6052498320984765</v>
+        <v>0.6613550005069615</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.101721594831133</v>
+        <v>-1.196860705612002</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.436776767787093</v>
+        <v>2.379693301318571</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.963908313709519</v>
+        <v>-5.823645392688306</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6930842336720131</v>
+        <v>0.7491894020804981</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.101721594831133</v>
+        <v>-1.196860705612002</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.417971026570888</v>
+        <v>2.360887560102367</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712292</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.723477816904659</v>
+        <v>-5.583214895883446</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7909995090188344</v>
+        <v>0.8471046774273194</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8612910980262725</v>
+        <v>-0.9564302088071419</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.563972401278682</v>
+        <v>2.50688893481016</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837682</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.480687009255213</v>
+        <v>-5.340424088234</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8920451459134329</v>
+        <v>0.9481503143219179</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8612910980262725</v>
+        <v>-0.9564302088071419</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.567901715113502</v>
+        <v>2.510818248644981</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.241081917648124</v>
+        <v>-5.100818996626911</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9885657664736085</v>
+        <v>1.044670934882094</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7942431503577779</v>
+        <v>-0.8893822611386474</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.608809067631939</v>
+        <v>2.551725601163417</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972337</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.99842632922496</v>
+        <v>-4.858163408203747</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.082626073062867</v>
+        <v>1.138731241471353</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7942431503577779</v>
+        <v>-0.8893822611386474</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.605807138851932</v>
+        <v>2.548723672383411</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145935</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.77840553118795</v>
+        <v>-4.638142610166737</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.172213429288286</v>
+        <v>1.228318597696771</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6530233052897977</v>
+        <v>-0.7481624160706671</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.692118082903335</v>
+        <v>2.635034616434813</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.579156901283141</v>
+        <v>-4.438893980261928</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.267807064052033</v>
+        <v>1.323912232460518</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6530233052897977</v>
+        <v>-0.7481624160706671</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.708012265705158</v>
+        <v>2.650928799236636</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.419641797763771</v>
+        <v>-4.279378876742558</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.332758949900082</v>
+        <v>1.388864118308568</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4935082017704278</v>
+        <v>-0.5886473125512972</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.804867172257082</v>
+        <v>2.74778370578856</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046992</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.274969652664034</v>
+        <v>-4.134706731642821</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.400715910501417</v>
+        <v>1.456821078909903</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3488360566706903</v>
+        <v>-0.4439751674515598</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.901758561878364</v>
+        <v>2.844675095409842</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412097</v>
       </c>
       <c r="C1933" t="n">
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.257200193733078</v>
+        <v>-4.116937272711865</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.323163386160521</v>
+        <v>1.379268554569006</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3310665977397348</v>
+        <v>-0.4262057085206042</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.827759929323659</v>
+        <v>2.770676462855137</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.76264390214451</v>
       </c>
       <c r="C1934" t="n">
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.170400695954068</v>
+        <v>-4.030137774932856</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.380283678594691</v>
+        <v>1.436388847003176</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3310665977397348</v>
+        <v>-0.4262057085206042</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.850160422646225</v>
+        <v>2.793076956177703</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.070708081225057</v>
+        <v>-3.930445160203844</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.420233125859708</v>
+        <v>1.476338294268193</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.231373983010723</v>
+        <v>-0.3265130937915925</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.910048392857044</v>
+        <v>2.852964926388522</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473596</v>
       </c>
       <c r="C1936" t="n">
         <v>3.05987970513818</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.773780022203414</v>
+        <v>-3.998815346527854</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.550011271943067</v>
+        <v>1.459997142213291</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.2108353359733297</v>
+        <v>-0.3172373947553775</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.186380906722178</v>
+        <v>2.869537268284954</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.736182382997127</v>
+        <v>3.362996724583694</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.161299661277118</v>
+        <v>2.879433372894097</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.773780022203414</v>
+        <v>-3.998815346527854</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.550011271943067</v>
+        <v>1.459997142213291</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.2108353359733297</v>
+        <v>-0.3172373947553775</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.154363458263486</v>
+        <v>2.872497169880465</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240417.xlsx
+++ b/tame_output/ON/bt/strategyON_20240417.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-46.8%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-15.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.7%</t>
+          <t>118.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.9%</t>
+          <t>138.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.4%</t>
+          <t>-58.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>780.2%</t>
+          <t>780.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-561.5%</t>
+          <t>-571.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.7%</t>
+          <t>-45.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-101.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-230.2%</t>
+          <t>-234.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.8%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-332.5%</t>
+          <t>-327.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-39.4%</t>
+          <t>-39.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-160.0%</t>
+          <t>-158.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-255.7%</t>
+          <t>-248.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-199.9%</t>
+          <t>-196.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-158.8%</t>
+          <t>-151.0%</t>
         </is>
       </c>
     </row>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.034375742069188</v>
+        <v>-1.980426917934219</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.316236135345659</v>
+        <v>2.337815664999647</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1970111525192294</v>
+        <v>0.2509599766541984</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.24854954799862</v>
+        <v>3.280918842479601</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.527700613604366</v>
+        <v>-2.473751789469397</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.127004937140156</v>
+        <v>2.148584466794144</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.09202503827961067</v>
+        <v>0.1459738624145797</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.193656629863417</v>
+        <v>3.226025924344398</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.020085641628463</v>
+        <v>-2.966136817493494</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.93115731797425</v>
+        <v>1.952736847628238</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4003599897444861</v>
+        <v>-0.3464111656095171</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.899332005092691</v>
+        <v>2.931701299573673</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.405266032558536</v>
+        <v>-3.351317208423567</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.775627700415084</v>
+        <v>1.797207230069072</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4003599897444861</v>
+        <v>-0.3464111656095171</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.897874543905555</v>
+        <v>2.930243838386536</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.748948805785199</v>
+        <v>-3.69499998165023</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.639923714579035</v>
+        <v>1.661503244233023</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.5082660417717042</v>
+        <v>-0.4543172176367353</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.83490003614384</v>
+        <v>2.867269330624821</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.106599156023547</v>
+        <v>-4.052650331888578</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.492969633139954</v>
+        <v>1.514549162793942</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.8659163920100523</v>
+        <v>-0.8119675678750834</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.616415884657089</v>
+        <v>2.64878517913807</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.415833259019598</v>
+        <v>-4.361884434884629</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.371048918641793</v>
+        <v>1.392628448295781</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.8659163920100523</v>
+        <v>-0.8119675678750834</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.618188811357348</v>
+        <v>2.65055810583833</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.847639052169385</v>
+        <v>-4.793690228034416</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.184659488849283</v>
+        <v>1.20623901850327</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.002333888451319</v>
+        <v>-0.9483850643163504</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.522671200959993</v>
+        <v>2.555040495440974</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.174071581037129</v>
+        <v>-5.12012275690216</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.042371252304275</v>
+        <v>1.063950781958263</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.084802138958467</v>
+        <v>-1.030853314823499</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.461475025657794</v>
+        <v>2.493844320138776</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.509734228267582</v>
+        <v>-5.455785404132612</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9066867850680596</v>
+        <v>0.9282663147220473</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.084802138958467</v>
+        <v>-1.030853314823499</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.460055617313759</v>
+        <v>2.492424911794741</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.873360473167895</v>
+        <v>-5.819411649032926</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7677238473421761</v>
+        <v>0.7893033769961635</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.183023775825593</v>
+        <v>-1.129074951690624</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.407610195427726</v>
+        <v>2.439979489908707</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.238487855806642</v>
+        <v>-6.184539031671672</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6209274092925088</v>
+        <v>0.6425069389464961</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.479334560124606</v>
+        <v>-1.425385735989637</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.229078239854149</v>
+        <v>2.261447534335131</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.64707663298732</v>
+        <v>-6.593127808852351</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4562534424349964</v>
+        <v>0.4778329720889838</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.833974513170315</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.982686517560501</v>
+        <v>2.015055812041483</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.060059117128413</v>
+        <v>-7.006110292993445</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2862458812500197</v>
+        <v>0.3078254109040071</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.833974513170315</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.977871950031962</v>
+        <v>2.010241244512943</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.476450991415411</v>
+        <v>-7.422502167280443</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.117683182144098</v>
+        <v>0.1392627117980854</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.833974513170315</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.975866000640839</v>
+        <v>2.008235295121821</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.853128001945255</v>
+        <v>-7.799179177810287</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.02272893139916077</v>
+        <v>-0.001149401745173417</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.833974513170315</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.986124691309518</v>
+        <v>2.0184939857905</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.199002823930064</v>
+        <v>-8.145053999795095</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.164979295047389</v>
+        <v>-0.1433997653934016</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.833974513170315</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.982224256455214</v>
+        <v>2.014593550936195</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.511827623175042</v>
+        <v>-8.457878799040074</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2917042946903794</v>
+        <v>-0.270124765036392</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.887923337305284</v>
+        <v>-1.833974513170315</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.980629176510215</v>
+        <v>2.012998470991196</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.808488964985241</v>
+        <v>-8.754540140850272</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4065898554852505</v>
+        <v>-0.3850103258312632</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.956666473039163</v>
+        <v>-1.902717648904194</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.943162270999096</v>
+        <v>1.975531565480077</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.241838073095476</v>
+        <v>-9.187889248960508</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.583955803263748</v>
+        <v>-0.5623762736097606</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.956666473039163</v>
+        <v>-1.902717648904194</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.939135966464693</v>
+        <v>1.971505260945674</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.624839461838107</v>
+        <v>-9.570890637703139</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7372584600823844</v>
+        <v>-0.715678930428397</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.956666473039163</v>
+        <v>-1.902717648904194</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.939033865143108</v>
+        <v>1.97140315962409</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.999824788009384</v>
+        <v>-9.945875963874416</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8846810745794653</v>
+        <v>-0.863101544925478</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.33165179921044</v>
+        <v>-2.277702975075471</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.716614185411772</v>
+        <v>1.748983479892753</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.35935511051339</v>
+        <v>-10.30540628637842</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.023142900283015</v>
+        <v>-1.001563370629028</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.33165179921044</v>
+        <v>-2.277702975075471</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.721964488709822</v>
+        <v>1.754333783190804</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.6857551391784</v>
+        <v>-10.63180631504343</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.145786891791844</v>
+        <v>-1.124207362137856</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.658051827875453</v>
+        <v>-2.604103003740484</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.534040491467992</v>
+        <v>1.566409785948973</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.9049041072526</v>
+        <v>-10.85095528311763</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.230404728399753</v>
+        <v>-1.208825198745766</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.877200795949651</v>
+        <v>-2.823251971814682</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.405592861245242</v>
+        <v>1.437962155726224</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.90121318229619</v>
+        <v>-10.84726435816122</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.22892835841719</v>
+        <v>-1.207348828763202</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.877200795949651</v>
+        <v>-2.823251971814682</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.405592861245242</v>
+        <v>1.437962155726224</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.10547135762605</v>
+        <v>-11.05152253349108</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.305118431430492</v>
+        <v>-1.283538901776505</v>
       </c>
       <c r="F1878" t="n">
-        <v>-3.00483974056364</v>
+        <v>-2.950890916428671</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.334522691595491</v>
+        <v>1.366891986076473</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.32350912925723</v>
+        <v>-11.26956030512226</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.387850985598527</v>
+        <v>-1.36627145594454</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.179610508659539</v>
+        <v>-3.125661684524569</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.234142785222388</v>
+        <v>1.26651207970337</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.25003929758978</v>
+        <v>-11.19609047345481</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.343091351438127</v>
+        <v>-1.32151182178414</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.10614067699209</v>
+        <v>-3.052191852857121</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.293596385716278</v>
+        <v>1.32596568019726</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078594</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.42516371497632</v>
+        <v>-11.37121489084135</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.398585897645227</v>
+        <v>-1.37700636799124</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.281265094378634</v>
+        <v>-3.227316270243665</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.203076956031869</v>
+        <v>1.23544625051285</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880266</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.65961580899081</v>
+        <v>-11.60566698485584</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.499585900152619</v>
+        <v>-1.478006370498632</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.281265094378634</v>
+        <v>-3.227316270243665</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.195857791130273</v>
+        <v>1.228227085611254</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.48068891723439</v>
+        <v>3.480688917234391</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.94741965352805</v>
+        <v>-11.89347082939308</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.621379628741491</v>
+        <v>-1.599800099087503</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.569068938915872</v>
+        <v>-3.515120114780903</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.016503293633954</v>
+        <v>1.048872588114935</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.49371243886058</v>
+        <v>3.493712438860581</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.17724410069187</v>
+        <v>-12.12329527655691</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.712193617768464</v>
+        <v>-1.690614088114477</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.731716475986033</v>
+        <v>-3.677767651851064</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9200305612304134</v>
+        <v>0.9523998557113953</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767394</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.40927302042814</v>
+        <v>-12.35532419629317</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.802311457033854</v>
+        <v>-1.780731927379867</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.793729173174456</v>
+        <v>-3.739780349039487</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.8855166715464744</v>
+        <v>0.9178859660274559</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.35725750645932</v>
+        <v>-12.30330868232435</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.777514915759928</v>
+        <v>-1.755935386105941</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.793729173174456</v>
+        <v>-3.739780349039487</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.8895070072328752</v>
+        <v>0.9218763017138567</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.49892934818344</v>
+        <v>-12.44498052404847</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.835658879348318</v>
+        <v>-1.814079349694331</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.793729173174456</v>
+        <v>-3.739780349039487</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.8880317803341335</v>
+        <v>0.920401074815115</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.59783608864272</v>
+        <v>-12.54388726450775</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.860168165367156</v>
+        <v>-1.838588635713168</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.892635913633731</v>
+        <v>-3.838687089498762</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8437411462234405</v>
+        <v>0.876110440704422</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.39868398140562</v>
+        <v>-12.34473515727065</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.793558456119</v>
+        <v>-1.771978926465013</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.727313387683918</v>
+        <v>-3.673364563548949</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9298835281466458</v>
+        <v>0.9622528226276272</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.17283882868621</v>
+        <v>-12.27380031292968</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.693641321995027</v>
+        <v>-1.734025915692415</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.685386712096754</v>
+        <v>-3.614086138779835</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.9646186065351525</v>
+        <v>1.007398950525304</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.88656401636351</v>
+        <v>-11.98752550060698</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.57799225250989</v>
+        <v>-1.618376846207278</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.685386712096754</v>
+        <v>-3.614086138779835</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.9657577510912114</v>
+        <v>1.008538095081363</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.9394593044078</v>
+        <v>-12.04042078865127</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.596516593565497</v>
+        <v>-1.636901187262885</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.680431366008308</v>
+        <v>-3.609130792691389</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.9713647329063866</v>
+        <v>1.014145076896538</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.65555057347905</v>
+        <v>-11.75651205772252</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.477219396955361</v>
+        <v>-1.517603990652749</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.680431366008308</v>
+        <v>-3.609130792691389</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.9770984371450231</v>
+        <v>1.019878781135175</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.4085633232861</v>
+        <v>-11.50952480752957</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.388161759272045</v>
+        <v>-1.428546352969433</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.362143542498437</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.115553524866929</v>
+        <v>1.158333868857081</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.14472645608203</v>
+        <v>-11.2456879403255</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.292510493703325</v>
+        <v>-1.332895087400713</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.362143542498437</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.105670043554022</v>
+        <v>1.148450387544173</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.87748465521363</v>
+        <v>-10.9784461394571</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.187448333855339</v>
+        <v>-1.227832927552728</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.433444115815356</v>
+        <v>-3.362143542498437</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.103835483054648</v>
+        <v>1.146615827044799</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.60167549181315</v>
+        <v>-10.70263697605662</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.077424983468606</v>
+        <v>-1.117809577165995</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.344424807536623</v>
+        <v>-3.273124234219703</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.156946753048427</v>
+        <v>1.199727097038579</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.57772195083719</v>
+        <v>-10.67868343508066</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.067175060932729</v>
+        <v>-1.107559654630118</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.320471266560665</v>
+        <v>-3.249170693243746</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.171987383779495</v>
+        <v>1.214767727769647</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.31366201251439</v>
+        <v>-10.41462349675786</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9748114017653631</v>
+        <v>-1.015195995462751</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.056411328237869</v>
+        <v>-2.98511075492095</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.317163030611421</v>
+        <v>1.359943374601572</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309723</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.606582389009557</v>
+        <v>-9.707543873253027</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6947665860237291</v>
+        <v>-0.7351511797211172</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.056411328237869</v>
+        <v>-2.98511075492095</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.31437599695112</v>
+        <v>1.357156340941271</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858726</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.566398090643366</v>
+        <v>-9.667359574886836</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6783492427894116</v>
+        <v>-0.7187338364867997</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.016227029871678</v>
+        <v>-2.944926456554759</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.338830199858676</v>
+        <v>1.381610543848827</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.486328295105562</v>
+        <v>-9.587289779349032</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6469545033535327</v>
+        <v>-0.6873390970509208</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.936157234333874</v>
+        <v>-2.864856661016955</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.386238898402115</v>
+        <v>1.429019242392267</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.252847072875962</v>
+        <v>-9.353808557119432</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5456375856238407</v>
+        <v>-0.5860221793212288</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.702676012104276</v>
+        <v>-2.631375438787356</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.534252060577727</v>
+        <v>1.577032404567878</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.073138542732089</v>
+        <v>-9.174100026975559</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4766463838792503</v>
+        <v>-0.5170309775766384</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.64550450794158</v>
+        <v>-2.574203934624661</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.565662752762385</v>
+        <v>1.608443096752536</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.940863069101201</v>
+        <v>-9.041824553344672</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4283687076798683</v>
+        <v>-0.4687533013772565</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.513229034310693</v>
+        <v>-2.441928460993774</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.640395523687944</v>
+        <v>1.683175867678095</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.750263394428048</v>
+        <v>-8.851224878671518</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3493137771229704</v>
+        <v>-0.3896983708203585</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.322629359637541</v>
+        <v>-2.251328786320622</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.757570389179472</v>
+        <v>1.800350733169624</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.501263595744467</v>
+        <v>-8.602225079987937</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2368075164258792</v>
+        <v>-0.2771921101232673</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.322629359637541</v>
+        <v>-2.251328786320622</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.770476730403131</v>
+        <v>1.813257074393282</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.606853585517571</v>
+        <v>-8.707815069761041</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4070194419343398</v>
+        <v>-0.4474040356317275</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.428219349410645</v>
+        <v>-2.356918776093726</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.579146806940049</v>
+        <v>1.621927150930201</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.480844023348592</v>
+        <v>-8.726549971879638</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3080712751896613</v>
+        <v>-0.4063536546020803</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.428219349410645</v>
+        <v>-2.356918776093726</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.627691148817136</v>
+        <v>1.670471492807287</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.204105848677779</v>
+        <v>-8.449811797208826</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1939969933353418</v>
+        <v>-0.2922793727477604</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.246402688300719</v>
+        <v>-2.1751021149838</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.740160157469086</v>
+        <v>1.782940501459237</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.077213442242709</v>
+        <v>-8.322919390773755</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1519540170147917</v>
+        <v>-0.2502363964272103</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.119510281865649</v>
+        <v>-2.04820970854873</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.80758161507665</v>
+        <v>1.850361959066801</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.033665035472017</v>
+        <v>-8.279370984003064</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1414952664016083</v>
+        <v>-0.2397776458140268</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.119510281865649</v>
+        <v>-2.04820970854873</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.800621002981557</v>
+        <v>1.843401346971708</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.791516642018159</v>
+        <v>-8.037222590549206</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.03017355463892191</v>
+        <v>-0.1284559340513405</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.119510281865649</v>
+        <v>-2.04820970854873</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.8150833573627</v>
+        <v>1.857863701352851</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.728287270249811</v>
+        <v>-7.973993218780858</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.01034968547238746</v>
+        <v>-0.1086320648848065</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.119510281865649</v>
+        <v>-2.04820970854873</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.809615477821895</v>
+        <v>1.852395821812046</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.541799577872805</v>
+        <v>-7.787505526403852</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.06174348548899156</v>
+        <v>-0.03653889392342702</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.933022589488643</v>
+        <v>-1.861722016171724</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.919006187258675</v>
+        <v>1.961786531248827</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.520650378969362</v>
+        <v>-7.766356327500408</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.07790414328769479</v>
+        <v>-0.02037823612472422</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.9118733905852</v>
+        <v>-1.840572817268281</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.939396684838067</v>
+        <v>1.982177028828219</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.276884936985917</v>
+        <v>-7.522590885516964</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1711910284281228</v>
+        <v>0.07290864901570426</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.9118733905852</v>
+        <v>-1.840572817268281</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.935177393185118</v>
+        <v>1.977957737175269</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.012856869792657</v>
+        <v>-7.258562818323703</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.278926569225443</v>
+        <v>0.1806441898130244</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.710007991769246</v>
+        <v>-1.638707418452327</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.058420946394706</v>
+        <v>2.101201290384857</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.763006475843582</v>
+        <v>-7.008712424374629</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3716088017887751</v>
+        <v>0.2733264223763565</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.710007991769246</v>
+        <v>-1.638707418452327</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.051163021378408</v>
+        <v>2.093943365368559</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.603393035819901</v>
+        <v>-6.70514493537065</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4390533013188964</v>
+        <v>0.3983525414985967</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.710007991769246</v>
+        <v>-1.638707418452327</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.054762144899057</v>
+        <v>2.097542488889208</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.529913126967887</v>
+        <v>-6.631665026518636</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4817727709142554</v>
+        <v>0.4410720110939561</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.636528082917232</v>
+        <v>-1.565227509600313</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.112177596264819</v>
+        <v>2.15495794025497</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102776</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.304880127299064</v>
+        <v>-6.406632026849813</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5708064483980815</v>
+        <v>0.5301056885777822</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.411495083248409</v>
+        <v>-1.34019450993149</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.24621787368241</v>
+        <v>2.288998217672561</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.76461430435307</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.090245749662658</v>
+        <v>-6.191997649213406</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6613550005069615</v>
+        <v>0.6206542406866622</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.196860705612002</v>
+        <v>-1.125560132295083</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.379693301318571</v>
+        <v>2.422473645308723</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544778</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.823645392688306</v>
+        <v>-5.925397292239055</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7491894020804981</v>
+        <v>0.7084886422601988</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.196860705612002</v>
+        <v>-1.125560132295083</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.360887560102367</v>
+        <v>2.403667904092518</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.583214895883446</v>
+        <v>-5.684966795434194</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8471046774273194</v>
+        <v>0.8064039176070201</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9564302088071419</v>
+        <v>-0.8851296354902227</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.50688893481016</v>
+        <v>2.549669278800312</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837681</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.340424088234</v>
+        <v>-5.442175987784749</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9481503143219179</v>
+        <v>0.9074495545016186</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9564302088071419</v>
+        <v>-0.8851296354902227</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.510818248644981</v>
+        <v>2.553598592635132</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.100818996626911</v>
+        <v>-5.20257089617766</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.044670934882094</v>
+        <v>1.003970175061794</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8893822611386474</v>
+        <v>-0.8180816878217282</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.551725601163417</v>
+        <v>2.594505945153569</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.848613050972337</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.858163408203747</v>
+        <v>-4.959915307754496</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.138731241471353</v>
+        <v>1.098030481651053</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8893822611386474</v>
+        <v>-0.8180816878217282</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.548723672383411</v>
+        <v>2.591504016373562</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145935</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.638142610166737</v>
+        <v>-4.739894509717486</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.228318597696771</v>
+        <v>1.187617837876471</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7481624160706671</v>
+        <v>-0.6768618427537479</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.635034616434813</v>
+        <v>2.677814960424965</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.438893980261928</v>
+        <v>-4.540645879812677</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.323912232460518</v>
+        <v>1.283211472640218</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7481624160706671</v>
+        <v>-0.6768618427537479</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.650928799236636</v>
+        <v>2.693709143226788</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.279378876742558</v>
+        <v>-4.381130776293307</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.388864118308568</v>
+        <v>1.348163358488268</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5886473125512972</v>
+        <v>-0.517346739234378</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.74778370578856</v>
+        <v>2.790564049778712</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046992</v>
       </c>
       <c r="C1932" t="n">
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.134706731642821</v>
+        <v>-4.236458631193569</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.456821078909903</v>
+        <v>1.416120319089603</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4439751674515598</v>
+        <v>-0.3726745941346406</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.844675095409842</v>
+        <v>2.887455439399994</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412097</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.116937272711865</v>
+        <v>-4.218689172262613</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.379268554569006</v>
+        <v>1.338567794748707</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4262057085206042</v>
+        <v>-0.3549051352036851</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.770676462855137</v>
+        <v>2.813456806845289</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264390214451</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.030137774932856</v>
+        <v>-4.131889674483604</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.436388847003176</v>
+        <v>1.395688087182877</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4262057085206042</v>
+        <v>-0.3549051352036851</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.793076956177703</v>
+        <v>2.835857300167855</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.930445160203844</v>
+        <v>-4.032197059754592</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.476338294268193</v>
+        <v>1.435637534447894</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3265130937915925</v>
+        <v>-0.2552125204746733</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.852964926388522</v>
+        <v>2.895745270378674</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473596</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.05987970513818</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.998815346527854</v>
+        <v>-4.100567246078603</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.459997142213291</v>
+        <v>1.419296382392992</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3172373947553775</v>
+        <v>-0.2459368214384584</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.869537268284954</v>
+        <v>2.912317612275105</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.362996724583694</v>
+        <v>3.368158997775824</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.879433372894097</v>
+        <v>2.957014380885813</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.998815346527854</v>
+        <v>-4.100567246078603</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.459997142213291</v>
+        <v>1.419296382392992</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3172373947553775</v>
+        <v>-0.2459368214384584</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.872497169880465</v>
+        <v>2.950078177872181</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240417.xlsx
+++ b/tame_output/ON/bt/strategyON_20240417.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -661,27 +661,27 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-46.8%</t>
+          <t>-45.2%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,35 +811,35 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.5%</t>
+          <t>117.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>138.4%</t>
+          <t>136.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.2%</t>
+          <t>-57.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>780.0%</t>
+          <t>789.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-571.6%</t>
+          <t>-539.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.5%</t>
+          <t>-45.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>5357.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-234.3%</t>
+          <t>-221.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-29.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-327.1%</t>
+          <t>-319.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-39.1%</t>
+          <t>-38.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.9%</t>
+          <t>-159.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-248.6%</t>
+          <t>-242.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-196.6%</t>
+          <t>-192.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-151.0%</t>
+          <t>-120.3%</t>
         </is>
       </c>
     </row>
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.980426917934219</v>
+        <v>-2.034375742069188</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.337815664999647</v>
+        <v>2.316236135345659</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.2509599766541984</v>
+        <v>0.1970111525192294</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.280918842479601</v>
+        <v>3.24854954799862</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.473751789469397</v>
+        <v>-2.30561866424424</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.148584466794144</v>
+        <v>2.215837716884207</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1459738624145797</v>
+        <v>0.22075377757333</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.226025924344398</v>
+        <v>3.270893873439649</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.966136817493494</v>
+        <v>-2.798003692268336</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.952736847628238</v>
+        <v>2.019990097718301</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3464111656095171</v>
+        <v>-0.2716312504507667</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.931701299573673</v>
+        <v>2.976569248668923</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.351317208423567</v>
+        <v>-3.183184083198409</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.797207230069072</v>
+        <v>1.864460480159135</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3464111656095171</v>
+        <v>-0.2716312504507667</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.930243838386536</v>
+        <v>2.975111787481786</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.69499998165023</v>
+        <v>-3.526866856425072</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.661503244233023</v>
+        <v>1.728756494323086</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4543172176367353</v>
+        <v>-0.3795373024779849</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.867269330624821</v>
+        <v>2.912137279720072</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.052650331888578</v>
+        <v>-3.88451720666342</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.514549162793942</v>
+        <v>1.581802412884004</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.8119675678750834</v>
+        <v>-0.737187652716333</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.64878517913807</v>
+        <v>2.69365312823332</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.361884434884629</v>
+        <v>-4.19375130965947</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.392628448295781</v>
+        <v>1.459881698385844</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.8119675678750834</v>
+        <v>-0.737187652716333</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.65055810583833</v>
+        <v>2.69542605493358</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.793690228034416</v>
+        <v>-4.625557102809258</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.20623901850327</v>
+        <v>1.273492268593333</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.9483850643163504</v>
+        <v>-0.8736051491576</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.555040495440974</v>
+        <v>2.599908444536224</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.12012275690216</v>
+        <v>-4.951989631677002</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.063950781958263</v>
+        <v>1.131204032048326</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.030853314823499</v>
+        <v>-0.9560733996647481</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.493844320138776</v>
+        <v>2.538712269234026</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.455785404132612</v>
+        <v>-5.287652278907454</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9282663147220473</v>
+        <v>0.9955195648121102</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.030853314823499</v>
+        <v>-0.9560733996647481</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.492424911794741</v>
+        <v>2.537292860889991</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.819411649032926</v>
+        <v>-5.651278523807767</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7893033769961635</v>
+        <v>0.8565566270862268</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.129074951690624</v>
+        <v>-1.054295036531874</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.439979489908707</v>
+        <v>2.484847439003957</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.184539031671672</v>
+        <v>-6.016405906446514</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6425069389464961</v>
+        <v>0.7097601890365595</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.425385735989637</v>
+        <v>-1.350605820830886</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.261447534335131</v>
+        <v>2.306315483430381</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.593127808852351</v>
+        <v>-6.424994683627193</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4778329720889838</v>
+        <v>0.5450862221790467</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.833974513170315</v>
+        <v>-1.759194598011565</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.015055812041483</v>
+        <v>2.059923761136733</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.006110292993445</v>
+        <v>-6.837977167768287</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3078254109040071</v>
+        <v>0.3750786609940699</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.833974513170315</v>
+        <v>-1.759194598011565</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.010241244512943</v>
+        <v>2.055109193608194</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.422502167280443</v>
+        <v>-7.254369042055284</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1392627117980854</v>
+        <v>0.2065159618881482</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.833974513170315</v>
+        <v>-1.759194598011565</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.008235295121821</v>
+        <v>2.053103244217071</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.799179177810287</v>
+        <v>-7.631046052585129</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.001149401745173417</v>
+        <v>0.06610384834488947</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.833974513170315</v>
+        <v>-1.759194598011565</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.0184939857905</v>
+        <v>2.06336193488575</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.145053999795095</v>
+        <v>-7.976920874569937</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1433997653934016</v>
+        <v>-0.07614651530333871</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.833974513170315</v>
+        <v>-1.759194598011565</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.014593550936195</v>
+        <v>2.059461500031445</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.457878799040074</v>
+        <v>-8.289745673814917</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.270124765036392</v>
+        <v>-0.2028715149463292</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.833974513170315</v>
+        <v>-1.759194598011565</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.012998470991196</v>
+        <v>2.057866420086446</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.754540140850272</v>
+        <v>-8.586407015625115</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3850103258312632</v>
+        <v>-0.3177570757412003</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.902717648904194</v>
+        <v>-1.827937733745443</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.975531565480077</v>
+        <v>2.020399514575328</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.187889248960508</v>
+        <v>-9.01975612373535</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5623762736097606</v>
+        <v>-0.4951230235196977</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.902717648904194</v>
+        <v>-1.827937733745443</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.971505260945674</v>
+        <v>2.016373210040924</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.570890637703139</v>
+        <v>-9.402757512477981</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.715678930428397</v>
+        <v>-0.6484256803383341</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.902717648904194</v>
+        <v>-1.827937733745443</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.97140315962409</v>
+        <v>2.01627110871934</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.945875963874416</v>
+        <v>-9.777742838649258</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.863101544925478</v>
+        <v>-0.7958482948354146</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.277702975075471</v>
+        <v>-2.202923059916721</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.748983479892753</v>
+        <v>1.793851428988004</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.30540628637842</v>
+        <v>-10.13727316115326</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.001563370629028</v>
+        <v>-0.9343101205389654</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.277702975075471</v>
+        <v>-2.202923059916721</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.754333783190804</v>
+        <v>1.799201732286054</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.63180631504343</v>
+        <v>-10.46367318981827</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.124207362137856</v>
+        <v>-1.056954112047793</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.604103003740484</v>
+        <v>-2.529323088581734</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.566409785948973</v>
+        <v>1.611277735044223</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.85095528311763</v>
+        <v>-10.68282215789247</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.208825198745766</v>
+        <v>-1.141571948655703</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.823251971814682</v>
+        <v>-2.748472056655932</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.437962155726224</v>
+        <v>1.482830104821474</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.84726435816122</v>
+        <v>-10.67913123293606</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.207348828763202</v>
+        <v>-1.140095578673139</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.823251971814682</v>
+        <v>-2.748472056655932</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.437962155726224</v>
+        <v>1.482830104821474</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.05152253349108</v>
+        <v>-10.88338940826592</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.283538901776505</v>
+        <v>-1.216285651686442</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.950890916428671</v>
+        <v>-2.87611100126992</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.366891986076473</v>
+        <v>1.411759935171723</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.26956030512226</v>
+        <v>-11.1014271798971</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.36627145594454</v>
+        <v>-1.299018205854477</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.125661684524569</v>
+        <v>-3.050881769365819</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.26651207970337</v>
+        <v>1.311380028798619</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.19609047345481</v>
+        <v>-11.02795734822965</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.32151182178414</v>
+        <v>-1.254258571694076</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.052191852857121</v>
+        <v>-2.977411937698371</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.32596568019726</v>
+        <v>1.37083362929251</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.37121489084135</v>
+        <v>-11.2030817656162</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.37700636799124</v>
+        <v>-1.309753117901177</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.227316270243665</v>
+        <v>-3.152536355084915</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.23544625051285</v>
+        <v>1.2803141996081</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.60566698485584</v>
+        <v>-11.43753385963069</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.478006370498632</v>
+        <v>-1.410753120408569</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.227316270243665</v>
+        <v>-3.152536355084915</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.228227085611254</v>
+        <v>1.273095034706504</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.89347082939308</v>
+        <v>-11.72533770416792</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.599800099087503</v>
+        <v>-1.53254684899744</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.515120114780903</v>
+        <v>-3.440340199622153</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.048872588114935</v>
+        <v>1.093740537210185</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.12329527655691</v>
+        <v>-11.95516215133175</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.690614088114477</v>
+        <v>-1.623360838024414</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.677767651851064</v>
+        <v>-3.602987736692314</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9523998557113953</v>
+        <v>0.9972678048066452</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.35532419629317</v>
+        <v>-12.18719107106801</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.780731927379867</v>
+        <v>-1.713478677289805</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.739780349039487</v>
+        <v>-3.665000433880737</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9178859660274559</v>
+        <v>0.9627539151227058</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.30330868232435</v>
+        <v>-12.1351755570992</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.755935386105941</v>
+        <v>-1.688682136015878</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.739780349039487</v>
+        <v>-3.665000433880737</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9218763017138567</v>
+        <v>0.9667442508091066</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.44498052404847</v>
+        <v>-12.27684739882332</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.814079349694331</v>
+        <v>-1.746826099604267</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.739780349039487</v>
+        <v>-3.665000433880737</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.920401074815115</v>
+        <v>0.965269023910365</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.54388726450775</v>
+        <v>-12.37575413928259</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.838588635713168</v>
+        <v>-1.771335385623106</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.838687089498762</v>
+        <v>-3.763907174340012</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.876110440704422</v>
+        <v>0.9209783897996724</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.34473515727065</v>
+        <v>-12.17660203204549</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.771978926465013</v>
+        <v>-1.704725676374949</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.673364563548949</v>
+        <v>-3.598584648390199</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9622528226276272</v>
+        <v>1.007120771722877</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.27380031292968</v>
+        <v>-11.95075687932608</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.734025915692415</v>
+        <v>-1.604808542250975</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.614086138779835</v>
+        <v>-3.556657972803035</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.007398950525304</v>
+        <v>1.041855850111384</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.98752550060698</v>
+        <v>-11.66448206700339</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.618376846207278</v>
+        <v>-1.489159472765838</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.614086138779835</v>
+        <v>-3.556657972803035</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.008538095081363</v>
+        <v>1.042994994667443</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-12.04042078865127</v>
+        <v>-11.71737735504767</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.636901187262885</v>
+        <v>-1.507683813821446</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.609130792691389</v>
+        <v>-3.551702626714589</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.014145076896538</v>
+        <v>1.048601976482618</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.75651205772252</v>
+        <v>-11.43346862411892</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.517603990652749</v>
+        <v>-1.388386617211309</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.609130792691389</v>
+        <v>-3.551702626714589</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.019878781135175</v>
+        <v>1.054335680721255</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.50952480752957</v>
+        <v>-11.18648137392597</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.428546352969433</v>
+        <v>-1.299328979527994</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.362143542498437</v>
+        <v>-3.304715376521637</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.158333868857081</v>
+        <v>1.192790768443161</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.2456879403255</v>
+        <v>-10.9226445067219</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.332895087400713</v>
+        <v>-1.203677713959274</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.362143542498437</v>
+        <v>-3.304715376521637</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.148450387544173</v>
+        <v>1.182907287130253</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.9784461394571</v>
+        <v>-10.65540270585351</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.227832927552728</v>
+        <v>-1.098615554111289</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.362143542498437</v>
+        <v>-3.304715376521637</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.146615827044799</v>
+        <v>1.181072726630879</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.70263697605662</v>
+        <v>-10.37959354245302</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.117809577165995</v>
+        <v>-0.9885922037245556</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.273124234219703</v>
+        <v>-3.215696068242903</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.199727097038579</v>
+        <v>1.234183996624659</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.67868343508066</v>
+        <v>-10.35564000147706</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.107559654630118</v>
+        <v>-0.9783422811886786</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.249170693243746</v>
+        <v>-3.191742527266946</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.214767727769647</v>
+        <v>1.249224627355727</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.41462349675786</v>
+        <v>-10.09158006315427</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.015195995462751</v>
+        <v>-0.8859786220213124</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.98511075492095</v>
+        <v>-2.92768258894415</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.359943374601572</v>
+        <v>1.394400274187652</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.707543873253027</v>
+        <v>-9.384500439649429</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7351511797211172</v>
+        <v>-0.605933806279678</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.98511075492095</v>
+        <v>-2.92768258894415</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.357156340941271</v>
+        <v>1.391613240527351</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.667359574886836</v>
+        <v>-9.344316141283239</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7187338364867997</v>
+        <v>-0.5895164630453604</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.944926456554759</v>
+        <v>-2.887498290577959</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.381610543848827</v>
+        <v>1.416067443434907</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.587289779349032</v>
+        <v>-9.264246345745434</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6873390970509208</v>
+        <v>-0.5581217236094815</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.864856661016955</v>
+        <v>-2.807428495040155</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.429019242392267</v>
+        <v>1.463476141978347</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.353808557119432</v>
+        <v>-9.030765123515835</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5860221793212288</v>
+        <v>-0.4568048058797896</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.631375438787356</v>
+        <v>-2.573947272810556</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.577032404567878</v>
+        <v>1.611489304153958</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.174100026975559</v>
+        <v>-8.851056593371961</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5170309775766384</v>
+        <v>-0.3878136041351992</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.574203934624661</v>
+        <v>-2.51677576864786</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.608443096752536</v>
+        <v>1.642899996338617</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.041824553344672</v>
+        <v>-8.718781119741074</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4687533013772565</v>
+        <v>-0.3395359279358172</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.441928460993774</v>
+        <v>-2.384500295016974</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.683175867678095</v>
+        <v>1.717632767264175</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.851224878671518</v>
+        <v>-8.52818144506792</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3896983708203585</v>
+        <v>-0.2604809973789193</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.251328786320622</v>
+        <v>-2.193900620343821</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.800350733169624</v>
+        <v>1.834807632755704</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.602225079987937</v>
+        <v>-8.279181646384339</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2771921101232673</v>
+        <v>-0.147974736681828</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.251328786320622</v>
+        <v>-2.193900620343821</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.813257074393282</v>
+        <v>1.847713973979362</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.707815069761041</v>
+        <v>-8.384771636157444</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4474040356317275</v>
+        <v>-0.3181866621902887</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.356918776093726</v>
+        <v>-2.299490610116926</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.621927150930201</v>
+        <v>1.656384050516281</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.726549971879638</v>
+        <v>-8.403506538276041</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4063536546020803</v>
+        <v>-0.277136281160641</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.356918776093726</v>
+        <v>-2.299490610116926</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.670471492807287</v>
+        <v>1.704928392393367</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.449811797208826</v>
+        <v>-8.126768363605228</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2922793727477604</v>
+        <v>-0.1630619993063211</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.1751021149838</v>
+        <v>-2.117673949007</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.782940501459237</v>
+        <v>1.817397401045318</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.322919390773755</v>
+        <v>-7.999875957170158</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2502363964272103</v>
+        <v>-0.1210190229857715</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.04820970854873</v>
+        <v>-1.99078154257193</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.850361959066801</v>
+        <v>1.884818858652881</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.279370984003064</v>
+        <v>-7.956327550399467</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2397776458140268</v>
+        <v>-0.1105602723725885</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.04820970854873</v>
+        <v>-1.99078154257193</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.843401346971708</v>
+        <v>1.877858246557788</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.037222590549206</v>
+        <v>-7.714179156945609</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1284559340513405</v>
+        <v>0.0007614393900978733</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.04820970854873</v>
+        <v>-1.99078154257193</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.857863701352851</v>
+        <v>1.892320600938931</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.973993218780858</v>
+        <v>-7.650949785177261</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1086320648848065</v>
+        <v>0.02058530855663232</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.04820970854873</v>
+        <v>-1.99078154257193</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.852395821812046</v>
+        <v>1.886852721398126</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.787505526403852</v>
+        <v>-7.464462092800255</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.03653889392342702</v>
+        <v>0.09267847951801178</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.861722016171724</v>
+        <v>-1.804293850194924</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.961786531248827</v>
+        <v>1.996243430834907</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.766356327500408</v>
+        <v>-7.443312893896811</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.02037823612472422</v>
+        <v>0.1088391373167146</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.840572817268281</v>
+        <v>-1.783144651291481</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.982177028828219</v>
+        <v>2.016633928414298</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.522590885516964</v>
+        <v>-7.199547451913367</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.07290864901570426</v>
+        <v>0.2021260224571431</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.840572817268281</v>
+        <v>-1.783144651291481</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.977957737175269</v>
+        <v>2.012414636761349</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.258562818323703</v>
+        <v>-6.935519384720108</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1806441898130244</v>
+        <v>0.3098615632544628</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.638707418452327</v>
+        <v>-1.581279252475527</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.101201290384857</v>
+        <v>2.135658189970937</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.008712424374629</v>
+        <v>-6.685668990771033</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2733264223763565</v>
+        <v>0.4025437958177949</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.638707418452327</v>
+        <v>-1.581279252475527</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.093943365368559</v>
+        <v>2.12840026495464</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.70514493537065</v>
+        <v>-6.382101501767054</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3983525414985967</v>
+        <v>0.527569914940035</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.638707418452327</v>
+        <v>-1.581279252475527</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.097542488889208</v>
+        <v>2.131999388475288</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862983</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.631665026518636</v>
+        <v>-6.30862159291504</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4410720110939561</v>
+        <v>0.5702893845353945</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.565227509600313</v>
+        <v>-1.507799343623513</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.15495794025497</v>
+        <v>2.189414839841051</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102778</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.406632026849813</v>
+        <v>-6.083588593246217</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5301056885777822</v>
+        <v>0.6593230620192205</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.34019450993149</v>
+        <v>-1.28276634395469</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.288998217672561</v>
+        <v>2.323455117258641</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461430435307</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.191997649213406</v>
+        <v>-5.86895421560981</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6206542406866622</v>
+        <v>0.7498716141281005</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.125560132295083</v>
+        <v>-1.068131966318283</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.422473645308723</v>
+        <v>2.456930544894803</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544778</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.925397292239055</v>
+        <v>-5.602353858635459</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7084886422601988</v>
+        <v>0.8377060157016372</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.125560132295083</v>
+        <v>-1.068131966318283</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.403667904092518</v>
+        <v>2.438124803678599</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.797691308712292</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.684966795434194</v>
+        <v>-5.361923361830598</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8064039176070201</v>
+        <v>0.9356212910484585</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8851296354902227</v>
+        <v>-0.8277014695134226</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.549669278800312</v>
+        <v>2.584126178386392</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837681</v>
+        <v>3.821589933837682</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.442175987784749</v>
+        <v>-5.119132554181153</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9074495545016186</v>
+        <v>1.036666927943057</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8851296354902227</v>
+        <v>-0.8277014695134226</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.553598592635132</v>
+        <v>2.588055492221212</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.20257089617766</v>
+        <v>-4.879527462574064</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.003970175061794</v>
+        <v>1.133187548503233</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8180816878217282</v>
+        <v>-0.7606535218449281</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.594505945153569</v>
+        <v>2.628962844739649</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.959915307754496</v>
+        <v>-4.6368718741509</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.098030481651053</v>
+        <v>1.227247855092491</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8180816878217282</v>
+        <v>-0.7606535218449281</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.591504016373562</v>
+        <v>2.625960915959642</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.739894509717486</v>
+        <v>-4.41685107611389</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.187617837876471</v>
+        <v>1.31683521131791</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6768618427537479</v>
+        <v>-0.6194336767769478</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.677814960424965</v>
+        <v>2.712271860011044</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.540645879812677</v>
+        <v>-4.217602446209081</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.283211472640218</v>
+        <v>1.412428846081657</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6768618427537479</v>
+        <v>-0.6194336767769478</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.693709143226788</v>
+        <v>2.728166042812868</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.381130776293307</v>
+        <v>-4.058087342689711</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.348163358488268</v>
+        <v>1.477380731929707</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.517346739234378</v>
+        <v>-0.4599185732575779</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.790564049778712</v>
+        <v>2.825020949364792</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.236458631193569</v>
+        <v>-3.913415197589973</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.416120319089603</v>
+        <v>1.545337692531041</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3726745941346406</v>
+        <v>-0.3152464281578405</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.887455439399994</v>
+        <v>2.921912338986074</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.218689172262613</v>
+        <v>-3.895645738659018</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.338567794748707</v>
+        <v>1.467785168190145</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3549051352036851</v>
+        <v>-0.2974769692268849</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.813456806845289</v>
+        <v>2.847913706431369</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.131889674483604</v>
+        <v>-3.808846240880009</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.395688087182877</v>
+        <v>1.524905460624315</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3549051352036851</v>
+        <v>-0.2974769692268849</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.835857300167855</v>
+        <v>2.870314199753935</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.032197059754592</v>
+        <v>-3.709153626150997</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.435637534447894</v>
+        <v>1.564854907889332</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2552125204746733</v>
+        <v>-0.1977843544978732</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.895745270378674</v>
+        <v>2.930202169964754</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.05987970513818</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.100567246078603</v>
+        <v>-3.777523812475007</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.419296382392992</v>
+        <v>1.54851375583443</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2459368214384584</v>
+        <v>-0.1885086554616582</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.912317612275105</v>
+        <v>2.946774511861185</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.368158997775824</v>
+        <v>3.859722470929794</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.957014380885813</v>
+        <v>3.264519424929272</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.100567246078603</v>
+        <v>-3.777523812475007</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.419296382392992</v>
+        <v>1.54851375583443</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2459368214384584</v>
+        <v>-0.1885086554616582</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.950078177872181</v>
+        <v>3.25758322191564</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240417.xlsx
+++ b/tame_output/ON/bt/strategyON_20240417.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>117.8%</t>
+          <t>118.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.4%</t>
+          <t>136.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>789.1%</t>
+          <t>788.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-539.3%</t>
+          <t>-540.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5357.4%</t>
+          <t>5368.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-221.4%</t>
+          <t>-200.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.6%</t>
+          <t>-157.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-242.8%</t>
+          <t>-233.5%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-120.3%</t>
+          <t>-124.2%</t>
         </is>
       </c>
     </row>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078594</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880266</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234391</v>
+        <v>3.48068891723439</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860581</v>
+        <v>3.49371243886058</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.839370871858726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862983</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.30862159291504</v>
+        <v>-6.206630198608703</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5702893845353945</v>
+        <v>0.6110859422579291</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.507799343623513</v>
+        <v>-1.405807949317176</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.189414839841051</v>
+        <v>2.250609676424852</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102778</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.083588593246217</v>
+        <v>-5.98159719893988</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6593230620192205</v>
+        <v>0.7001196197417552</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.28276634395469</v>
+        <v>-1.180774949648353</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.323455117258641</v>
+        <v>2.384649953842443</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.76461430435307</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.86895421560981</v>
+        <v>-5.766962821303474</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7498716141281005</v>
+        <v>0.7906681718506352</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.068131966318283</v>
+        <v>-0.9661405720119465</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.456930544894803</v>
+        <v>2.518125381478605</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544778</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.602353858635459</v>
+        <v>-5.500362464329122</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8377060157016372</v>
+        <v>0.8785025734241718</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.068131966318283</v>
+        <v>-0.9661405720119465</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.438124803678599</v>
+        <v>2.4993196402624</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712292</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.361923361830598</v>
+        <v>-5.259931967524262</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9356212910484585</v>
+        <v>0.9764178487709931</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8277014695134226</v>
+        <v>-0.7257100752070862</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.584126178386392</v>
+        <v>2.645321014970194</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837682</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.119132554181153</v>
+        <v>-5.017141159874816</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.036666927943057</v>
+        <v>1.077463485665592</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8277014695134226</v>
+        <v>-0.7257100752070862</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.588055492221212</v>
+        <v>2.649250328805014</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.879527462574064</v>
+        <v>-4.777536068267727</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.133187548503233</v>
+        <v>1.173984106225767</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7606535218449281</v>
+        <v>-0.6586621275385917</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.628962844739649</v>
+        <v>2.690157681323451</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972337</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.6368718741509</v>
+        <v>-4.534880479844563</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.227247855092491</v>
+        <v>1.268044412815026</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7606535218449281</v>
+        <v>-0.6586621275385917</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.625960915959642</v>
+        <v>2.687155752543444</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145935</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.41685107611389</v>
+        <v>-4.314859681807553</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.31683521131791</v>
+        <v>1.357631769040444</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6194336767769478</v>
+        <v>-0.5174422824706114</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.712271860011044</v>
+        <v>2.773466696594846</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.217602446209081</v>
+        <v>-4.115611051902744</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.412428846081657</v>
+        <v>1.453225403804191</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6194336767769478</v>
+        <v>-0.5174422824706114</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.728166042812868</v>
+        <v>2.78936087939667</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.058087342689711</v>
+        <v>-3.956095948383374</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.477380731929707</v>
+        <v>1.518177289652241</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4599185732575779</v>
+        <v>-0.3579271789512415</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.825020949364792</v>
+        <v>2.886215785948593</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046992</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.913415197589973</v>
+        <v>-3.811423803283637</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.545337692531041</v>
+        <v>1.586134250253576</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3152464281578405</v>
+        <v>-0.2132550338515041</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.921912338986074</v>
+        <v>2.983107175569876</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412097</v>
       </c>
       <c r="C1933" t="n">
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.895645738659018</v>
+        <v>-3.793654344352681</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.467785168190145</v>
+        <v>1.50858172591268</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2974769692268849</v>
+        <v>-0.1954855749205485</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.847913706431369</v>
+        <v>2.909108543015171</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.76264390214451</v>
       </c>
       <c r="C1934" t="n">
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.808846240880009</v>
+        <v>-3.706854846573672</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.524905460624315</v>
+        <v>1.56570201834685</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2974769692268849</v>
+        <v>-0.1954855749205485</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.870314199753935</v>
+        <v>2.931509036337737</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.709153626150997</v>
+        <v>-3.607162231844661</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.564854907889332</v>
+        <v>1.605651465611866</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1977843544978732</v>
+        <v>-0.09579296019153677</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.930202169964754</v>
+        <v>2.991397006548556</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473596</v>
       </c>
       <c r="C1936" t="n">
         <v>3.05987970513818</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.777523812475007</v>
+        <v>-3.67553241816867</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.54851375583443</v>
+        <v>1.589310313556964</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1885086554616582</v>
+        <v>-0.08651726115532182</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.946774511861185</v>
+        <v>3.007969348444987</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.859722470929794</v>
+        <v>3.720439619178368</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.264519424929272</v>
+        <v>3.274996948852618</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.777523812475007</v>
+        <v>-3.790503512097386</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.54851375583443</v>
+        <v>1.758439119699917</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1885086554616582</v>
+        <v>-0.09472750745537944</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.25758322191564</v>
+        <v>3.218160444379391</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240417.xlsx
+++ b/tame_output/ON/bt/strategyON_20240417.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -661,17 +661,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-46.7%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>-6.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>118.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.6%</t>
+          <t>138.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.5%</t>
+          <t>-58.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>788.1%</t>
+          <t>780.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-540.6%</t>
+          <t>-563.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.0%</t>
+          <t>-45.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5368.0%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-200.4%</t>
+          <t>-232.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-319.6%</t>
+          <t>-332.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-39.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.1%</t>
+          <t>-160.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-233.5%</t>
+          <t>-238.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-192.2%</t>
+          <t>-199.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-124.2%</t>
+          <t>-149.5%</t>
         </is>
       </c>
     </row>
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.30561866424424</v>
+        <v>-2.527700613604366</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.215837716884207</v>
+        <v>2.127004937140156</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.22075377757333</v>
+        <v>0.09202503827961067</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.270893873439649</v>
+        <v>3.193656629863417</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.798003692268336</v>
+        <v>-3.020085641628463</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.019990097718301</v>
+        <v>1.93115731797425</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.2716312504507667</v>
+        <v>-0.4003599897444861</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.976569248668923</v>
+        <v>2.899332005092691</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.183184083198409</v>
+        <v>-3.405266032558536</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.864460480159135</v>
+        <v>1.775627700415084</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.2716312504507667</v>
+        <v>-0.4003599897444861</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.975111787481786</v>
+        <v>2.897874543905555</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.526866856425072</v>
+        <v>-3.748948805785199</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.728756494323086</v>
+        <v>1.639923714579035</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3795373024779849</v>
+        <v>-0.5082660417717042</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.912137279720072</v>
+        <v>2.83490003614384</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.88451720666342</v>
+        <v>-4.106599156023547</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.581802412884004</v>
+        <v>1.492969633139954</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.737187652716333</v>
+        <v>-0.8659163920100523</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.69365312823332</v>
+        <v>2.616415884657089</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.19375130965947</v>
+        <v>-4.415833259019598</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.459881698385844</v>
+        <v>1.371048918641793</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.737187652716333</v>
+        <v>-0.8659163920100523</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.69542605493358</v>
+        <v>2.618188811357348</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.625557102809258</v>
+        <v>-4.847639052169385</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.273492268593333</v>
+        <v>1.184659488849283</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8736051491576</v>
+        <v>-1.002333888451319</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.599908444536224</v>
+        <v>2.522671200959993</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.951989631677002</v>
+        <v>-5.174071581037129</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.131204032048326</v>
+        <v>1.042371252304275</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9560733996647481</v>
+        <v>-1.084802138958467</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.538712269234026</v>
+        <v>2.461475025657794</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.287652278907454</v>
+        <v>-5.509734228267582</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9955195648121102</v>
+        <v>0.9066867850680596</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9560733996647481</v>
+        <v>-1.084802138958467</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.537292860889991</v>
+        <v>2.460055617313759</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.651278523807767</v>
+        <v>-5.873360473167895</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8565566270862268</v>
+        <v>0.7677238473421761</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.054295036531874</v>
+        <v>-1.183023775825593</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.484847439003957</v>
+        <v>2.407610195427726</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.016405906446514</v>
+        <v>-6.238487855806642</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.7097601890365595</v>
+        <v>0.6209274092925088</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.350605820830886</v>
+        <v>-1.479334560124606</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.306315483430381</v>
+        <v>2.229078239854149</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.424994683627193</v>
+        <v>-6.64707663298732</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5450862221790467</v>
+        <v>0.4562534424349964</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.759194598011565</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.059923761136733</v>
+        <v>1.982686517560501</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.837977167768287</v>
+        <v>-7.060059117128413</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3750786609940699</v>
+        <v>0.2862458812500197</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.759194598011565</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.055109193608194</v>
+        <v>1.977871950031962</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.254369042055284</v>
+        <v>-7.476450991415411</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2065159618881482</v>
+        <v>0.117683182144098</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.759194598011565</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.053103244217071</v>
+        <v>1.975866000640839</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.631046052585129</v>
+        <v>-7.853128001945255</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.06610384834488947</v>
+        <v>-0.02272893139916077</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.759194598011565</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.06336193488575</v>
+        <v>1.986124691309518</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.976920874569937</v>
+        <v>-8.199002823930064</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.07614651530333871</v>
+        <v>-0.164979295047389</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.759194598011565</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.059461500031445</v>
+        <v>1.982224256455214</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.289745673814917</v>
+        <v>-8.511827623175042</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2028715149463292</v>
+        <v>-0.2917042946903794</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.759194598011565</v>
+        <v>-1.887923337305284</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.057866420086446</v>
+        <v>1.980629176510215</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.586407015625115</v>
+        <v>-8.808488964985241</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3177570757412003</v>
+        <v>-0.4065898554852505</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.827937733745443</v>
+        <v>-1.956666473039163</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.020399514575328</v>
+        <v>1.943162270999096</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.01975612373535</v>
+        <v>-9.241838073095476</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4951230235196977</v>
+        <v>-0.583955803263748</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.827937733745443</v>
+        <v>-1.956666473039163</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.016373210040924</v>
+        <v>1.939135966464693</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.402757512477981</v>
+        <v>-9.624839461838107</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6484256803383341</v>
+        <v>-0.7372584600823844</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.827937733745443</v>
+        <v>-1.956666473039163</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.01627110871934</v>
+        <v>1.939033865143108</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.777742838649258</v>
+        <v>-9.999824788009384</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7958482948354146</v>
+        <v>-0.8846810745794653</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.202923059916721</v>
+        <v>-2.33165179921044</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.793851428988004</v>
+        <v>1.716614185411772</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.13727316115326</v>
+        <v>-10.35935511051339</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9343101205389654</v>
+        <v>-1.023142900283015</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.202923059916721</v>
+        <v>-2.33165179921044</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.799201732286054</v>
+        <v>1.721964488709822</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.46367318981827</v>
+        <v>-10.6857551391784</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.056954112047793</v>
+        <v>-1.145786891791844</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.529323088581734</v>
+        <v>-2.658051827875453</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.611277735044223</v>
+        <v>1.534040491467992</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.68282215789247</v>
+        <v>-10.9049041072526</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.141571948655703</v>
+        <v>-1.230404728399753</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.748472056655932</v>
+        <v>-2.877200795949651</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.482830104821474</v>
+        <v>1.405592861245242</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.67913123293606</v>
+        <v>-10.90121318229619</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.140095578673139</v>
+        <v>-1.22892835841719</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.748472056655932</v>
+        <v>-2.877200795949651</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.482830104821474</v>
+        <v>1.405592861245242</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.88338940826592</v>
+        <v>-11.10547135762605</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.216285651686442</v>
+        <v>-1.305118431430492</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.87611100126992</v>
+        <v>-3.00483974056364</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.411759935171723</v>
+        <v>1.334522691595491</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.1014271798971</v>
+        <v>-11.32350912925723</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.299018205854477</v>
+        <v>-1.387850985598527</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.050881769365819</v>
+        <v>-3.179610508659539</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.311380028798619</v>
+        <v>1.234142785222388</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.02795734822965</v>
+        <v>-11.25003929758978</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.254258571694076</v>
+        <v>-1.343091351438127</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.977411937698371</v>
+        <v>-3.10614067699209</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.37083362929251</v>
+        <v>1.293596385716278</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.2030817656162</v>
+        <v>-11.42516371497632</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.309753117901177</v>
+        <v>-1.398585897645227</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.152536355084915</v>
+        <v>-3.281265094378634</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.2803141996081</v>
+        <v>1.203076956031869</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.43753385963069</v>
+        <v>-11.65961580899081</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.410753120408569</v>
+        <v>-1.499585900152619</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.152536355084915</v>
+        <v>-3.281265094378634</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.273095034706504</v>
+        <v>1.195857791130273</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.72533770416792</v>
+        <v>-11.94741965352805</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.53254684899744</v>
+        <v>-1.621379628741491</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.440340199622153</v>
+        <v>-3.569068938915872</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.093740537210185</v>
+        <v>1.016503293633954</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.95516215133175</v>
+        <v>-12.17724410069187</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.623360838024414</v>
+        <v>-1.712193617768464</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.602987736692314</v>
+        <v>-3.731716475986033</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9972678048066452</v>
+        <v>0.9200305612304134</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.18719107106801</v>
+        <v>-12.40927302042814</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.713478677289805</v>
+        <v>-1.802311457033854</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.665000433880737</v>
+        <v>-3.793729173174456</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9627539151227058</v>
+        <v>0.8855166715464744</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.1351755570992</v>
+        <v>-12.35725750645932</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.688682136015878</v>
+        <v>-1.777514915759928</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.665000433880737</v>
+        <v>-3.793729173174456</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9667442508091066</v>
+        <v>0.8895070072328752</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.27684739882332</v>
+        <v>-12.49892934818344</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.746826099604267</v>
+        <v>-1.835658879348318</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.665000433880737</v>
+        <v>-3.793729173174456</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.965269023910365</v>
+        <v>0.8880317803341335</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.37575413928259</v>
+        <v>-12.59783608864272</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.771335385623106</v>
+        <v>-1.860168165367156</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.763907174340012</v>
+        <v>-3.892635913633731</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9209783897996724</v>
+        <v>0.8437411462234405</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.17660203204549</v>
+        <v>-12.39868398140562</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.704725676374949</v>
+        <v>-1.793558456119</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.598584648390199</v>
+        <v>-3.727313387683918</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.007120771722877</v>
+        <v>0.9298835281466458</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.95075687932608</v>
+        <v>-12.17283882868621</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.604808542250975</v>
+        <v>-1.693641321995027</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.556657972803035</v>
+        <v>-3.685386712096754</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.041855850111384</v>
+        <v>0.9646186065351525</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.66448206700339</v>
+        <v>-12.0649972242332</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.489159472765838</v>
+        <v>-1.649365535657765</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.556657972803035</v>
+        <v>-3.685386712096754</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.042994994667443</v>
+        <v>0.9657577510912114</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.71737735504767</v>
+        <v>-12.11789251227749</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.507683813821446</v>
+        <v>-1.667889876713372</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.551702626714589</v>
+        <v>-3.680431366008308</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.048601976482618</v>
+        <v>0.9713647329063866</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.43346862411892</v>
+        <v>-11.83398378134874</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.388386617211309</v>
+        <v>-1.548592680103236</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.551702626714589</v>
+        <v>-3.680431366008308</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.054335680721255</v>
+        <v>0.9770984371450231</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.18648137392597</v>
+        <v>-11.58699653115579</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.299328979527994</v>
+        <v>-1.459535042419921</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.304715376521637</v>
+        <v>-3.433444115815356</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.192790768443161</v>
+        <v>1.115553524866929</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.9226445067219</v>
+        <v>-11.32315966395172</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.203677713959274</v>
+        <v>-1.3638837768512</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.304715376521637</v>
+        <v>-3.433444115815356</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.182907287130253</v>
+        <v>1.105670043554022</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.65540270585351</v>
+        <v>-11.05591786308332</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.098615554111289</v>
+        <v>-1.258821617003214</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.304715376521637</v>
+        <v>-3.433444115815356</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.181072726630879</v>
+        <v>1.103835483054648</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.37959354245302</v>
+        <v>-10.78010869968284</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9885922037245556</v>
+        <v>-1.148798266616482</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.215696068242903</v>
+        <v>-3.344424807536623</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.234183996624659</v>
+        <v>1.156946753048427</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.35564000147706</v>
+        <v>-10.75615515870688</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9783422811886786</v>
+        <v>-1.138548344080605</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.191742527266946</v>
+        <v>-3.320471266560665</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.249224627355727</v>
+        <v>1.171987383779495</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.09158006315427</v>
+        <v>-10.49209522038408</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8859786220213124</v>
+        <v>-1.046184684913238</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.92768258894415</v>
+        <v>-3.056411328237869</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.394400274187652</v>
+        <v>1.317163030611421</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.384500439649429</v>
+        <v>-9.785015596879244</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.605933806279678</v>
+        <v>-0.7661398691716039</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.92768258894415</v>
+        <v>-3.056411328237869</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.391613240527351</v>
+        <v>1.31437599695112</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.344316141283239</v>
+        <v>-9.744831298513054</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5895164630453604</v>
+        <v>-0.7497225259372864</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.887498290577959</v>
+        <v>-3.016227029871678</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.416067443434907</v>
+        <v>1.338830199858676</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.264246345745434</v>
+        <v>-9.664761502975249</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5581217236094815</v>
+        <v>-0.7183277865014079</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.807428495040155</v>
+        <v>-2.936157234333874</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.463476141978347</v>
+        <v>1.386238898402115</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.030765123515835</v>
+        <v>-9.43128028074565</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4568048058797896</v>
+        <v>-0.6170108687717155</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.573947272810556</v>
+        <v>-2.702676012104276</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.611489304153958</v>
+        <v>1.534252060577727</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.851056593371961</v>
+        <v>-9.251571750601777</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3878136041351992</v>
+        <v>-0.5480196670271256</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.51677576864786</v>
+        <v>-2.64550450794158</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.642899996338617</v>
+        <v>1.565662752762385</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.718781119741074</v>
+        <v>-9.119296276970889</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3395359279358172</v>
+        <v>-0.4997419908277436</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.384500295016974</v>
+        <v>-2.513229034310693</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.717632767264175</v>
+        <v>1.640395523687944</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.52818144506792</v>
+        <v>-8.928696602297736</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2604809973789193</v>
+        <v>-0.4206870602708452</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.193900620343821</v>
+        <v>-2.322629359637541</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.834807632755704</v>
+        <v>1.757570389179472</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.279181646384339</v>
+        <v>-8.679696803614155</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.147974736681828</v>
+        <v>-0.3081807995737544</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.193900620343821</v>
+        <v>-2.322629359637541</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.847713973979362</v>
+        <v>1.770476730403131</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.384771636157444</v>
+        <v>-8.785286793387259</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3181866621902887</v>
+        <v>-0.4783927250822146</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.299490610116926</v>
+        <v>-2.428219349410645</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.656384050516281</v>
+        <v>1.579146806940049</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.403506538276041</v>
+        <v>-8.804021695505856</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.277136281160641</v>
+        <v>-0.437342344052567</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.299490610116926</v>
+        <v>-2.428219349410645</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.704928392393367</v>
+        <v>1.627691148817136</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.126768363605228</v>
+        <v>-8.527283520835043</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1630619993063211</v>
+        <v>-0.3232680621982476</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.117673949007</v>
+        <v>-2.246402688300719</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.817397401045318</v>
+        <v>1.740160157469086</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.999875957170158</v>
+        <v>-8.400391114399973</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1210190229857715</v>
+        <v>-0.2812250858776975</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.99078154257193</v>
+        <v>-2.119510281865649</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.884818858652881</v>
+        <v>1.80758161507665</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.956327550399467</v>
+        <v>-8.356842707629282</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1105602723725885</v>
+        <v>-0.270766335264514</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.99078154257193</v>
+        <v>-2.119510281865649</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.877858246557788</v>
+        <v>1.800621002981557</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.714179156945609</v>
+        <v>-8.114694314175424</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.0007614393900978733</v>
+        <v>-0.1594446235018276</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.99078154257193</v>
+        <v>-2.119510281865649</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.892320600938931</v>
+        <v>1.8150833573627</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.650949785177261</v>
+        <v>-8.051464942407076</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.02058530855663232</v>
+        <v>-0.1396207543352936</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.99078154257193</v>
+        <v>-2.119510281865649</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.886852721398126</v>
+        <v>1.809615477821895</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.464462092800255</v>
+        <v>-7.86497725003007</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.09267847951801178</v>
+        <v>-0.06752758337391462</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.804293850194924</v>
+        <v>-1.933022589488643</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.996243430834907</v>
+        <v>1.919006187258675</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.443312893896811</v>
+        <v>-7.843828051126627</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1088391373167146</v>
+        <v>-0.05136692557521139</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.783144651291481</v>
+        <v>-1.9118733905852</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.016633928414298</v>
+        <v>1.939396684838067</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.199547451913367</v>
+        <v>-7.600062609143182</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2021260224571431</v>
+        <v>0.0419199595652171</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.783144651291481</v>
+        <v>-1.9118733905852</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.012414636761349</v>
+        <v>1.935177393185118</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.935519384720108</v>
+        <v>-7.336034541949923</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3098615632544628</v>
+        <v>0.1496555003625368</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.581279252475527</v>
+        <v>-1.710007991769246</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.135658189970937</v>
+        <v>2.058420946394706</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.685668990771033</v>
+        <v>-7.086184148000848</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4025437958177949</v>
+        <v>0.2423377329258689</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.581279252475527</v>
+        <v>-1.710007991769246</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.12840026495464</v>
+        <v>2.051163021378408</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.382101501767054</v>
+        <v>-6.782616658996869</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.527569914940035</v>
+        <v>0.3673638520481091</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.581279252475527</v>
+        <v>-1.710007991769246</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.131999388475288</v>
+        <v>2.054762144899057</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.206630198608703</v>
+        <v>-6.709136750144856</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6110859422579291</v>
+        <v>0.4100833216434681</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.405807949317176</v>
+        <v>-1.636528082917232</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.250609676424852</v>
+        <v>2.112177596264819</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.98159719893988</v>
+        <v>-6.484103750476033</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7001196197417552</v>
+        <v>0.4991169991272946</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.180774949648353</v>
+        <v>-1.411495083248409</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.384649953842443</v>
+        <v>2.24621787368241</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.766962821303474</v>
+        <v>-6.269469372839626</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7906681718506352</v>
+        <v>0.5896655512361746</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9661405720119465</v>
+        <v>-1.196860705612002</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.518125381478605</v>
+        <v>2.379693301318571</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.500362464329122</v>
+        <v>-6.002869015865274</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8785025734241718</v>
+        <v>0.6774999528097108</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9661405720119465</v>
+        <v>-1.196860705612002</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.4993196402624</v>
+        <v>2.360887560102367</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.259931967524262</v>
+        <v>-5.762438519060414</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9764178487709931</v>
+        <v>0.7754152281565325</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7257100752070862</v>
+        <v>-0.9564302088071419</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.645321014970194</v>
+        <v>2.50688893481016</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.017141159874816</v>
+        <v>-5.519647711410968</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.077463485665592</v>
+        <v>0.8764608650511305</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7257100752070862</v>
+        <v>-0.9564302088071419</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.649250328805014</v>
+        <v>2.510818248644981</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.777536068267727</v>
+        <v>-5.280042619803879</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.173984106225767</v>
+        <v>0.9729814856113062</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6586621275385917</v>
+        <v>-0.8893822611386474</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.690157681323451</v>
+        <v>2.551725601163417</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.534880479844563</v>
+        <v>-5.037387031380716</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.268044412815026</v>
+        <v>1.067041792200565</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6586621275385917</v>
+        <v>-0.8893822611386474</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.687155752543444</v>
+        <v>2.548723672383411</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.314859681807553</v>
+        <v>-4.817366233343705</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.357631769040444</v>
+        <v>1.156629148425984</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5174422824706114</v>
+        <v>-0.7481624160706671</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.773466696594846</v>
+        <v>2.635034616434813</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.115611051902744</v>
+        <v>-4.618117603438896</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.453225403804191</v>
+        <v>1.252222783189731</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5174422824706114</v>
+        <v>-0.7481624160706671</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.78936087939667</v>
+        <v>2.650928799236636</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.956095948383374</v>
+        <v>-4.458602499919526</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.518177289652241</v>
+        <v>1.31717466903778</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3579271789512415</v>
+        <v>-0.5886473125512972</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.886215785948593</v>
+        <v>2.74778370578856</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.811423803283637</v>
+        <v>-4.313930354819789</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.586134250253576</v>
+        <v>1.385131629639115</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2132550338515041</v>
+        <v>-0.4439751674515598</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.983107175569876</v>
+        <v>2.844675095409842</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.793654344352681</v>
+        <v>-4.296160895888833</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.50858172591268</v>
+        <v>1.307579105298219</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1954855749205485</v>
+        <v>-0.4262057085206042</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.909108543015171</v>
+        <v>2.770676462855137</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.706854846573672</v>
+        <v>-4.209361398109824</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.56570201834685</v>
+        <v>1.364699397732389</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1954855749205485</v>
+        <v>-0.4262057085206042</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.931509036337737</v>
+        <v>2.793076956177703</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.607162231844661</v>
+        <v>-4.109668783380812</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.605651465611866</v>
+        <v>1.404648844997406</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.09579296019153677</v>
+        <v>-0.3265130937915925</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.991397006548556</v>
+        <v>2.852964926388522</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.05987970513818</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.67553241816867</v>
+        <v>-4.178038969704822</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.589310313556964</v>
+        <v>1.388307692942504</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.08651726115532182</v>
+        <v>-0.3172373947553775</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.007969348444987</v>
+        <v>2.869537268284954</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.720439619178368</v>
+        <v>3.369153640333397</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.274996948852618</v>
+        <v>3.050316413770071</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.790503512097386</v>
+        <v>-4.021712707953822</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.758439119699917</v>
+        <v>1.441274906274795</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.09472750745537944</v>
+        <v>-0.1422120995740162</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.218160444379391</v>
+        <v>2.964989154025662</v>
       </c>
     </row>
   </sheetData>
